--- a/Excels compiladores de habilidades/Habilidades de criaturas no humanoides.xlsx
+++ b/Excels compiladores de habilidades/Habilidades de criaturas no humanoides.xlsx
@@ -5,19 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\Rol\Plantilals de Unidades y Npcs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\arkanor-assets\Excels compiladores de habilidades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8621135B-7E8F-4417-8C80-4267FAAF8927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0F8B5D-E7C1-4DC9-AF63-6514988ED004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4E5D0542-3908-4101-9CFE-772E035496F2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Constructos" sheetId="7" r:id="rId1"/>
-    <sheet name="Infernales" sheetId="6" r:id="rId2"/>
-    <sheet name="Elementales" sheetId="5" r:id="rId3"/>
-    <sheet name="Bestias Definitivo" sheetId="2" r:id="rId4"/>
-    <sheet name="Ignotos" sheetId="3" r:id="rId5"/>
+    <sheet name="No-Muerto" sheetId="8" r:id="rId1"/>
+    <sheet name="Constructos" sheetId="7" r:id="rId2"/>
+    <sheet name="Infernales" sheetId="6" r:id="rId3"/>
+    <sheet name="Elementales" sheetId="5" r:id="rId4"/>
+    <sheet name="Bestias Definitivo" sheetId="2" r:id="rId5"/>
+    <sheet name="Ignotos" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
     <author>Lenovo</author>
   </authors>
   <commentList>
-    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{B02384FF-6D99-461A-8D4B-5F57D7CD5778}">
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{3A9A5688-723E-4473-986E-1C1C4FB84E8D}">
       <text>
         <r>
           <rPr>
@@ -57,7 +58,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{2062999C-9D1A-4BBB-ABA7-F40882AE5D7E}">
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{F51978EB-854D-4C28-8C6F-DF7DE74455C0}">
       <text>
         <r>
           <rPr>
@@ -81,7 +82,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{EA5A58FA-6633-4552-A84C-677BC68817C2}">
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{570239EC-0FFE-42BC-B9F6-D6C4CCCDD321}">
       <text>
         <r>
           <rPr>
@@ -105,7 +106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{3B5D69E7-6DCD-4F20-9594-B3400629E5ED}">
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{5334146D-9D40-411C-8B99-19AC41FC52DB}">
       <text>
         <r>
           <rPr>
@@ -130,7 +131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{6053E287-9BF8-4FE7-B4F6-BE5DD998A987}">
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{756E0E38-9B36-4010-A293-70247A10F12A}">
       <text>
         <r>
           <rPr>
@@ -155,7 +156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{C96F3801-4ECE-444C-BAD5-DA52CCF5EA65}">
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{EADF6322-808B-41D7-BDDA-004CCC7B054D}">
       <text>
         <r>
           <rPr>
@@ -180,7 +181,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{3961B8B5-5124-4FCA-91C1-19C4C1B31B39}">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{7B8CF153-62A3-4CE4-99E0-D983E839C6D3}">
       <text>
         <r>
           <rPr>
@@ -205,7 +206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{2C5F50B5-1A7F-45B6-94B2-EC5B5F773014}">
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{5A34DA84-2C2B-47D6-84AA-BD415A20D5B5}">
       <text>
         <r>
           <rPr>
@@ -231,7 +232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{00D3FF88-B685-4D6F-A78A-35A0E3A20A91}">
+    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{F0F1F6CD-A21A-46C4-A667-8592270D6BFD}">
       <text>
         <r>
           <rPr>
@@ -256,7 +257,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{C338C571-16C6-48D1-BC06-809F6E680796}">
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{AFF06013-45A8-4FE2-BA8B-75145A9FD686}">
       <text>
         <r>
           <rPr>
@@ -281,7 +282,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{94E84700-3187-4079-BE8B-8D4861D25384}">
+    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{6FFD7657-F31F-425B-A8F4-48E2404C6738}">
       <text>
         <r>
           <rPr>
@@ -306,7 +307,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{F70ADD31-8F01-48C2-B9C9-B4B59E53F1FE}">
+    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{740A5F90-F1A7-4C73-B994-41F1E7CB081E}">
       <text>
         <r>
           <rPr>
@@ -331,7 +332,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{C0727135-D077-4A11-AB93-DA5BB8AD416E}">
+    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{CA756A64-B30B-42F1-93E1-1EBAF6D9D99D}">
       <text>
         <r>
           <rPr>
@@ -355,7 +356,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{90CE00C9-FCEC-44C6-831A-CF0473D7124A}">
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{04840DC0-3739-49EA-9FC3-AF539C8323B2}">
       <text>
         <r>
           <rPr>
@@ -378,7 +379,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{E6FF0DB7-E9F6-4164-B338-C1174382A791}">
+    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{C5E685A4-EFD6-49F9-A16F-E992EAF3F502}">
       <text>
         <r>
           <rPr>
@@ -401,7 +402,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{42B2B8BB-21F8-44CE-83A2-676F58988D68}">
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{088C6471-F011-43DC-B6A4-BCA6355F1045}">
       <text>
         <r>
           <rPr>
@@ -426,7 +427,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{F3319603-96B8-4324-94B0-ECA9B3368B6A}">
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{1FB32786-7850-4BFB-961A-5D4CC4F6E6CB}">
       <text>
         <r>
           <rPr>
@@ -451,7 +452,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{AC8E2D4D-1B36-4A18-88F2-1F91E4CEF639}">
+    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{47F47C84-D882-4CB5-ADE3-19E73EA529D7}">
       <text>
         <r>
           <rPr>
@@ -476,7 +477,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{0D87D7E4-FF3A-4A71-BDBD-CE7DD78CFCCF}">
+    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{7BE878CB-44E2-469C-8EA2-DC2A83B3D126}">
       <text>
         <r>
           <rPr>
@@ -501,7 +502,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{F6769080-2631-4FD5-97C1-509168CCBEB3}">
+    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{04F8BA78-898D-4697-9736-9011A8CEA990}">
       <text>
         <r>
           <rPr>
@@ -526,7 +527,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{FF84C399-0EEA-4CE8-BE23-E3658315C840}">
+    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{58445964-79BB-4BC0-B097-8570C44441E2}">
       <text>
         <r>
           <rPr>
@@ -551,7 +552,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J5" authorId="0" shapeId="0" xr:uid="{82CAEF47-E93C-42C8-AC7C-4CCDFC29A139}">
+    <comment ref="J5" authorId="0" shapeId="0" xr:uid="{31FAD696-9DCF-498C-8FE6-F8CF5F1DAC0B}">
       <text>
         <r>
           <rPr>
@@ -577,7 +578,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K5" authorId="0" shapeId="0" xr:uid="{6F9F0887-3A62-496C-B4ED-94FAA897BCD6}">
+    <comment ref="K5" authorId="0" shapeId="0" xr:uid="{53DCF68B-01BD-4AAF-BBC8-BC745DB9DFCF}">
       <text>
         <r>
           <rPr>
@@ -603,7 +604,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L5" authorId="0" shapeId="0" xr:uid="{D0B8E48E-A848-47DD-B6FC-89634E723E85}">
+    <comment ref="L5" authorId="0" shapeId="0" xr:uid="{B1C5A739-5D00-4E8E-A446-3A8D9381BA73}">
       <text>
         <r>
           <rPr>
@@ -628,7 +629,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M5" authorId="0" shapeId="0" xr:uid="{1A613C4C-F51C-4D44-8E7A-7E4B93DEDA6E}">
+    <comment ref="M5" authorId="0" shapeId="0" xr:uid="{F3349975-F99C-428F-B16F-A18A62D95A25}">
       <text>
         <r>
           <rPr>
@@ -653,7 +654,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N5" authorId="0" shapeId="0" xr:uid="{29C46259-DD23-40E1-AACA-634F532B3663}">
+    <comment ref="N5" authorId="0" shapeId="0" xr:uid="{F0E71175-7BB8-4BA8-B641-6FA0B077B4AE}">
       <text>
         <r>
           <rPr>
@@ -677,7 +678,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{D45B507F-8BC4-436D-8C68-959DAE6D1734}">
+    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{1E51D271-AD49-4C0F-9574-36540A2028E9}">
       <text>
         <r>
           <rPr>
@@ -700,7 +701,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{15011769-4289-4A23-8F20-056B37682318}">
+    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{E5D24E2B-5D0D-4BF8-8909-865566927D27}">
       <text>
         <r>
           <rPr>
@@ -723,7 +724,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{91303DDA-DFE1-4F7E-ABA2-B49DDBE4BCC1}">
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{A5096B21-B71A-4B6F-BA1A-5D4E17A54836}">
       <text>
         <r>
           <rPr>
@@ -746,7 +747,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{48754531-5027-4449-825D-ED9E119A74F1}">
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{3C4F00BE-5CBA-488B-9AAE-1FA90BB7C3CF}">
       <text>
         <r>
           <rPr>
@@ -770,7 +771,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{FC5FCD31-A6AC-47D5-9CDA-F139D2D6E1B5}">
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{2C1EDACB-5DB1-4769-A88F-DE3F9EBF20BE}">
       <text>
         <r>
           <rPr>
@@ -793,7 +794,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{E72EA9EE-ACC7-4711-B3EF-F233BA1AF673}">
+    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{8A7F0B60-398E-45D9-85DC-5BBC51879026}">
       <text>
         <r>
           <rPr>
@@ -808,7 +809,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{CD6D2B3F-AFD8-4961-8B87-74779D7BC706}">
+    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{4783A463-FF26-406E-9A85-E2EBEE5EA06B}">
       <text>
         <r>
           <rPr>
@@ -833,7 +834,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{6DC56B03-868E-4725-8B6E-F141E3E7BA76}">
+    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{32FBA22B-C501-46D9-BAB8-BC64CF9D8131}">
       <text>
         <r>
           <rPr>
@@ -847,7 +848,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J8" authorId="0" shapeId="0" xr:uid="{F7F054FF-9704-4B40-9FBB-A9550487F43F}">
+    <comment ref="J8" authorId="0" shapeId="0" xr:uid="{6512C48F-F578-4BF5-87C2-DC1A3186C56A}">
       <text>
         <r>
           <rPr>
@@ -873,7 +874,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K8" authorId="0" shapeId="0" xr:uid="{6D75887A-C854-4259-AD4B-A62AA314F634}">
+    <comment ref="K8" authorId="0" shapeId="0" xr:uid="{4915BBF4-F08D-4FE2-8927-92AB29A8C93B}">
       <text>
         <r>
           <rPr>
@@ -898,7 +899,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{A16FB699-D3F4-4769-A3F5-56387F0EA4A3}">
+    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{0D5A4D1E-FF7F-4D71-8B85-D83528F51D2F}">
       <text>
         <r>
           <rPr>
@@ -933,7 +934,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{4B24683D-741B-4FFB-9E78-473C3142B5AF}">
+    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{78E4EC37-6014-4862-820C-9F8B648B8B41}">
       <text>
         <r>
           <rPr>
@@ -958,7 +959,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N8" authorId="0" shapeId="0" xr:uid="{10DF7389-214B-4F8B-B09B-42CA9D647A9D}">
+    <comment ref="N8" authorId="0" shapeId="0" xr:uid="{E5F5BA49-E73D-4511-A79A-005D2BB0D311}">
       <text>
         <r>
           <rPr>
@@ -982,7 +983,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{E8571940-7A3C-487B-B8D0-79C4E3809D32}">
+    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{78E6C8C9-EAFE-4A9C-9056-48D636C07404}">
       <text>
         <r>
           <rPr>
@@ -1006,7 +1007,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{0C1FC1C6-080D-44E8-9056-0EDBF239A2AD}">
+    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{EE5A695E-C02E-4B11-8458-6C9D9A683F95}">
       <text>
         <r>
           <rPr>
@@ -1029,7 +1030,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{BF3C6F3C-9B50-498B-AF64-8C7B5F3AFC84}">
+    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{982F2C87-4AD3-4845-A627-A745407A2E03}">
       <text>
         <r>
           <rPr>
@@ -1054,7 +1055,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{B99C26EC-A7F5-4C98-85B0-D49654BF7A88}">
+    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{C26A9823-1584-4EC6-81C9-A639DAFF8677}">
       <text>
         <r>
           <rPr>
@@ -1079,7 +1080,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{E5C8033C-33F3-42E5-AA93-85535EA5782D}">
+    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{490C739C-E3C1-4BE6-82B0-B12CEECA506C}">
       <text>
         <r>
           <rPr>
@@ -1104,7 +1105,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{741730A0-55A5-4871-BFBC-AB85A69D2328}">
+    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{4FE8FBA8-4A75-49F4-AE83-943AB7859CB4}">
       <text>
         <r>
           <rPr>
@@ -1129,22 +1130,22 @@
         </r>
       </text>
     </comment>
-    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{1934B238-DD2F-4F8D-B5C2-605CB128FDA2}">
+    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{8343D754-DA81-4657-B839-B992A23683C9}">
       <text/>
     </comment>
-    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{F4324D76-DB18-4EA0-80C8-A5D41BF6430C}">
+    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{85EF0248-AD1B-4BF7-8E48-69C07C1D0C7B}">
       <text/>
     </comment>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{536F1F09-498C-4CD7-ACBD-973ABAFC45A8}">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{379E51D2-473D-4147-B588-049E17223364}">
       <text/>
     </comment>
-    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{7873D641-930B-412C-99EB-ACCE1B6903BA}">
+    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{EB87A54C-0110-4CD9-A55F-E2B1DBA8C7C4}">
       <text/>
     </comment>
-    <comment ref="L11" authorId="0" shapeId="0" xr:uid="{CA592E41-51E8-4A0A-A770-D6BFB2D6692B}">
+    <comment ref="L11" authorId="0" shapeId="0" xr:uid="{8497B7E7-04B7-4616-B5E5-411A3A4876F5}">
       <text/>
     </comment>
-    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{CE60AD7E-E8F4-4842-AAC7-1183432930D8}">
+    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{32E152F1-B3AD-49E4-A1F1-2970C83D3BAC}">
       <text>
         <r>
           <rPr>
@@ -1169,7 +1170,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N11" authorId="0" shapeId="0" xr:uid="{E3551E66-1E47-46B4-8C3E-FAAF631527DD}">
+    <comment ref="N11" authorId="0" shapeId="0" xr:uid="{654F10F5-F1DC-46D8-9220-2A96CE68401F}">
       <text>
         <r>
           <rPr>
@@ -1193,7 +1194,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{C681949D-9CB6-4360-B779-65EF9A82937B}">
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{A837F313-9DB0-48EA-9C2E-76B6CDEDE617}">
       <text>
         <r>
           <rPr>
@@ -1216,7 +1217,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C14" authorId="0" shapeId="0" xr:uid="{B29B81D5-43CE-4EB9-84AE-47190CBC12B7}">
+    <comment ref="C14" authorId="0" shapeId="0" xr:uid="{1E4DBEDB-28C2-4346-A69E-E4680EB7BEFA}">
       <text>
         <r>
           <rPr>
@@ -1239,7 +1240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{F6D20034-E09F-4D0F-B6A1-4AAC6705055D}">
+    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{4C96FD4F-8B2C-49F8-8DB0-31DF2DE95EC9}">
       <text>
         <r>
           <rPr>
@@ -1262,7 +1263,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{465474A4-F5F6-41E3-8BEB-C090E0C03CE2}">
+    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{6B10C668-15C7-4F8B-9468-BD5AD878FBB7}">
       <text>
         <r>
           <rPr>
@@ -1287,7 +1288,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{9B9DF6E8-09FF-4CFB-96E4-FEC3B01C9263}">
+    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{F51FDF81-D553-4D19-AF6E-DADA6F0E981C}">
       <text>
         <r>
           <rPr>
@@ -1312,7 +1313,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{C20B36D6-BE34-42EA-869F-B4A5D2B4F87A}">
+    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{AE3B563E-B86F-447D-87A7-EE1F28D9A01C}">
       <text>
         <r>
           <rPr>
@@ -1337,7 +1338,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{85A181E2-BDCF-4871-A39F-746AF155793A}">
+    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{D126CC9F-FFC7-4760-97BA-F389D2535478}">
       <text>
         <r>
           <rPr>
@@ -1362,7 +1363,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{2DE3F587-72EF-415B-A1C7-AAEDFBB30E82}">
+    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{FD3C960E-0D46-4008-9562-D03F87E168DA}">
       <text>
         <r>
           <rPr>
@@ -1387,7 +1388,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{EDDBC006-AD5E-4397-9846-83DCB0FA70C2}">
+    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{BA000111-D2FF-4819-A8B9-C45B8EF7653A}">
       <text>
         <r>
           <rPr>
@@ -1412,7 +1413,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{50A10281-E822-4DCB-9087-F29592987F0F}">
+    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{A0E0B94B-0FB0-476C-9F4D-852772289E66}">
       <text>
         <r>
           <rPr>
@@ -1437,7 +1438,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L14" authorId="0" shapeId="0" xr:uid="{9F3F8902-AD57-461E-9AD3-D57079E82899}">
+    <comment ref="L14" authorId="0" shapeId="0" xr:uid="{FEBE5850-A3FF-4229-84A8-634A5849F905}">
       <text>
         <r>
           <rPr>
@@ -1462,7 +1463,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M14" authorId="0" shapeId="0" xr:uid="{3B9B4BD1-7ADC-42DD-94BD-A5A6F4D898FC}">
+    <comment ref="M14" authorId="0" shapeId="0" xr:uid="{66E98119-BD2B-4F73-8BAC-AC03E7E42F23}">
       <text>
         <r>
           <rPr>
@@ -1487,7 +1488,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N14" authorId="0" shapeId="0" xr:uid="{B417D6EC-DA7B-477E-AC62-A5FA7A90AFF5}">
+    <comment ref="N14" authorId="0" shapeId="0" xr:uid="{67096810-4685-424E-88E5-11EF2EB25ACF}">
       <text>
         <r>
           <rPr>
@@ -1522,53 +1523,54 @@
     <author>Lenovo</author>
   </authors>
   <commentList>
-    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{C7064E69-F89D-4397-AF2A-4022D65CFC09}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Posesión Infernal: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">La criatura realiza un ataque cuerpo a cuerpo que no produce daño pero intenta introducir su materia nubosa dentro de una criatura que no sea constructo, ignoto, celestial o arcano y controlarlo. Para que sea efectivo además de que la chance cuerpo a cuerpo sea exitosa, debe hacer tiradas d20 de inteligencia como parte de la misma acción principal, debe superar los puntos de vida actuales y los puntos de resilencia del objetivo sumados, si acumula tres fallos fallará en la posesión, si acumula tres éxitos el infernal se introduce completamente dentro de su víctima, esta convulsiona brevemente durante unos segundos y el infernal toma total control del cuerpo de la criatura y se vuelven una sola unidad, las estadísticas de FZA, AGI y CON son las de la víctima y CAR, INT y SAB del infernal. El objetivo no esta muerto, pero su consciencia se encuentra dormida, el infernal adopta la clase de este, añadiendo el tipo ignoto a los tipos que ya tiene y la inscripción "poseído/a" despues del nombre. 3 RES. </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{55A8DA2F-4870-4E20-8F41-AB141DE2BB42}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Baba Cegadora: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Ataque a distancia, la criatura lanza un escupitajo a un punto que pueda ver a 15 metros máximo de él, si el objetivo es otra criatura lo dirige directamente a los ojos. Si el ataque es exitoso el objetivo debe superar una tirada de salvación de Destreza CD 13 para no quedar cegadas hasta el final del siguiente turno del lanzador. 2 Res.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{FB95730E-D979-40CB-A11B-1E95813039DA}">
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{B02384FF-6D99-461A-8D4B-5F57D7CD5778}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Estructura Metálica: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(Pasivo) La criatura tiene defensas naturales otorgadas por los materíales metálicos que predominan en su forma que resultan en 19, 5, 22, 14, 23, 4. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{2062999C-9D1A-4BBB-ABA7-F40882AE5D7E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Automatísmo Arcano: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(pasivo) La unidad no se ve afectada por efectos que disminuya la RES o el MANÁ, ya que no posee estos, en su lugar posee lubricación y nucleo arcano. Cuando uno de estos llega a 0 por alguna razón el constructo automáticamente cesa su funcionamiento autónomo.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{EA5A58FA-6633-4552-A84C-677BC68817C2}">
       <text>
         <r>
           <rPr>
@@ -1578,7 +1580,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Profanar Vida: </t>
+          <t xml:space="preserve">Organismo Mecánico: </t>
         </r>
         <r>
           <rPr>
@@ -1587,11 +1589,12 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>(Conjuro) Extiende una extremidad hacia un objetivo y lanza un haz de luz oscura inmaterial (no puede ser bloqueado con elementos normales). Si golpea exitosamente al objetivo le hace daño de conjuro directo y ahora el taumaturgo puede dirigir esa misma cantidad de puntos hacia un cádaver que se encuentre a unos 15 metros de radio máximo del objetivo y al alcance de su vista. Éste es reanimado bajo el control del lanzador y se cura tantos puntos de vida como daño haya hecho al objetivo. 5 maná.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{46E47B66-CDE4-4E74-AA2A-16DE7A9A1D5F}">
+          <t xml:space="preserve">(Pasivo) El constructo no posee órganos biológicos de ningún ntipo, en su lugar está compúesto de partes mecánicas de diversa índole. Es inmune a efectos de aturdir, dormir, asustado, envenenado, emborrachado, cansado, incapacitado, inconsciente, no le afectan los encantamientos salvo excepciones aclaradas por el DM y no puede perder cordura. No puede ser sanado por métodos mágicos o primeros auxilios.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{3B5D69E7-6DCD-4F20-9594-B3400629E5ED}">
       <text>
         <r>
           <rPr>
@@ -1616,7 +1619,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{22542D72-98E4-4CB8-BEE3-A5C38C06008B}">
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{6053E287-9BF8-4FE7-B4F6-BE5DD998A987}">
       <text>
         <r>
           <rPr>
@@ -1641,7 +1644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{D3DC91B1-ADBB-47B4-8399-986C8A6E91F2}">
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{C96F3801-4ECE-444C-BAD5-DA52CCF5EA65}">
       <text>
         <r>
           <rPr>
@@ -1666,7 +1669,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{2FA71643-9FF5-42FD-9DB5-DEC155F493EE}">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{3961B8B5-5124-4FCA-91C1-19C4C1B31B39}">
       <text>
         <r>
           <rPr>
@@ -1691,7 +1694,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{B725D93C-9DC4-4A1F-AE39-5A05C638ED84}">
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{2C5F50B5-1A7F-45B6-94B2-EC5B5F773014}">
       <text>
         <r>
           <rPr>
@@ -1717,7 +1720,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{30537D8E-285F-4A1A-A94B-A6D03D89B1EC}">
+    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{00D3FF88-B685-4D6F-A78A-35A0E3A20A91}">
       <text>
         <r>
           <rPr>
@@ -1742,7 +1745,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{1E2C7054-9728-464F-9829-A8996FFDC9B7}">
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{C338C571-16C6-48D1-BC06-809F6E680796}">
       <text>
         <r>
           <rPr>
@@ -1767,7 +1770,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{97C05670-C8F3-438F-9622-998DC8BC8BE7}">
+    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{94E84700-3187-4079-BE8B-8D4861D25384}">
       <text>
         <r>
           <rPr>
@@ -1792,7 +1795,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{B174C16E-E14D-4FA8-88E3-82CC8395D8CD}">
+    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{F70ADD31-8F01-48C2-B9C9-B4B59E53F1FE}">
       <text>
         <r>
           <rPr>
@@ -1817,7 +1820,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{F55D79A1-6E9B-42A7-B56A-6EC79C20D044}">
+    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{C0727135-D077-4A11-AB93-DA5BB8AD416E}">
       <text>
         <r>
           <rPr>
@@ -1841,7 +1844,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{83D8ABA7-05CF-4D7F-AE7D-CF5D2980DA10}">
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{90CE00C9-FCEC-44C6-831A-CF0473D7124A}">
       <text>
         <r>
           <rPr>
@@ -1864,7 +1867,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{C66F9D7A-72A8-4E27-903D-8AC267EB767D}">
+    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{E6FF0DB7-E9F6-4164-B338-C1174382A791}">
       <text>
         <r>
           <rPr>
@@ -1887,7 +1890,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{8FBA1150-FB53-4226-80FB-92936C737BB8}">
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{42B2B8BB-21F8-44CE-83A2-676F58988D68}">
       <text>
         <r>
           <rPr>
@@ -1912,7 +1915,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{928F1912-4013-46B2-85EF-1B7E12A192B9}">
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{F3319603-96B8-4324-94B0-ECA9B3368B6A}">
       <text>
         <r>
           <rPr>
@@ -1937,7 +1940,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{B64DDE96-3F21-4346-B090-7590170B3729}">
+    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{AC8E2D4D-1B36-4A18-88F2-1F91E4CEF639}">
       <text>
         <r>
           <rPr>
@@ -1962,7 +1965,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{60670469-0035-445E-8723-E716D5308A33}">
+    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{0D87D7E4-FF3A-4A71-BDBD-CE7DD78CFCCF}">
       <text>
         <r>
           <rPr>
@@ -1987,7 +1990,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{02489D7C-4108-47E1-A81D-75AA18070D2A}">
+    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{F6769080-2631-4FD5-97C1-509168CCBEB3}">
       <text>
         <r>
           <rPr>
@@ -2012,7 +2015,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{4852E822-8987-479D-AEDB-72C5DC7FDE24}">
+    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{FF84C399-0EEA-4CE8-BE23-E3658315C840}">
       <text>
         <r>
           <rPr>
@@ -2037,7 +2040,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J5" authorId="0" shapeId="0" xr:uid="{B2E84B09-CAF5-4FFF-A744-33B13259AD69}">
+    <comment ref="J5" authorId="0" shapeId="0" xr:uid="{82CAEF47-E93C-42C8-AC7C-4CCDFC29A139}">
       <text>
         <r>
           <rPr>
@@ -2063,7 +2066,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K5" authorId="0" shapeId="0" xr:uid="{ACDCA6D2-8A0E-45B7-8527-74837936443C}">
+    <comment ref="K5" authorId="0" shapeId="0" xr:uid="{6F9F0887-3A62-496C-B4ED-94FAA897BCD6}">
       <text>
         <r>
           <rPr>
@@ -2089,7 +2092,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L5" authorId="0" shapeId="0" xr:uid="{CFE3E9DE-2A18-4A6F-8AB0-E89B97CD5C82}">
+    <comment ref="L5" authorId="0" shapeId="0" xr:uid="{D0B8E48E-A848-47DD-B6FC-89634E723E85}">
       <text>
         <r>
           <rPr>
@@ -2114,7 +2117,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M5" authorId="0" shapeId="0" xr:uid="{90CC3AA6-DDFB-46AF-ACB1-1E573C501B40}">
+    <comment ref="M5" authorId="0" shapeId="0" xr:uid="{1A613C4C-F51C-4D44-8E7A-7E4B93DEDA6E}">
       <text>
         <r>
           <rPr>
@@ -2139,7 +2142,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N5" authorId="0" shapeId="0" xr:uid="{3FB96D09-04B5-4BFE-9905-5B7CC59CEE92}">
+    <comment ref="N5" authorId="0" shapeId="0" xr:uid="{29C46259-DD23-40E1-AACA-634F532B3663}">
       <text>
         <r>
           <rPr>
@@ -2163,7 +2166,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{BD65E44B-A74C-4305-BE10-2F4AB954BD40}">
+    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{D45B507F-8BC4-436D-8C68-959DAE6D1734}">
       <text>
         <r>
           <rPr>
@@ -2186,7 +2189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{589C72F8-8CA0-4C38-B69B-49333637C527}">
+    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{15011769-4289-4A23-8F20-056B37682318}">
       <text>
         <r>
           <rPr>
@@ -2209,7 +2212,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{C5112136-BAF6-4452-99CC-2DE96F56FA3C}">
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{91303DDA-DFE1-4F7E-ABA2-B49DDBE4BCC1}">
       <text>
         <r>
           <rPr>
@@ -2232,7 +2235,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{DD6E6FBC-5BC9-4CF4-80FE-445FF748180D}">
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{48754531-5027-4449-825D-ED9E119A74F1}">
       <text>
         <r>
           <rPr>
@@ -2256,30 +2259,30 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{4B13328E-2E30-434E-A45D-77DC5FC28107}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Embestida Brutal: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Ataque precedido por la acción de movimiento la cual debe recorrer mínimamente 1 metro. Hace daño base en contundente con un bonus de 1d6 +1d6 por cada 4 puntos de CON. Si el ataque impacta o es bloqueado por el objetivo este debe hacer una tirada de CON vs la FZA del atacante, si falla es desplazado 2 metros, +1 por cada 5 puntos de fuerza del atacante, y queda derribado y aturdido por 1 turno. 3 RES.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{105A5A60-E262-4BB3-AFE6-D424DF476ACF}">
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{FC5FCD31-A6AC-47D5-9CDA-F139D2D6E1B5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Piel Pseudoescamoide: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Pasivo) La criatura tiene la piel cubierta por placas de costras endurecidas similares a escamas. Sus defensas naturales son 28, 19, 11, 32, 41, 5.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{E72EA9EE-ACC7-4711-B3EF-F233BA1AF673}">
       <text>
         <r>
           <rPr>
@@ -2294,7 +2297,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{E2889347-ABFB-4EB9-93B5-ECADEACD7677}">
+    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{CD6D2B3F-AFD8-4961-8B87-74779D7BC706}">
       <text>
         <r>
           <rPr>
@@ -2319,7 +2322,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{4FB4D028-EA9E-4B16-A78A-F23934D3EBB1}">
+    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{6DC56B03-868E-4725-8B6E-F141E3E7BA76}">
       <text>
         <r>
           <rPr>
@@ -2333,7 +2336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J8" authorId="0" shapeId="0" xr:uid="{97275EF5-3FE9-4DE0-BB89-6724A505DE0F}">
+    <comment ref="J8" authorId="0" shapeId="0" xr:uid="{F7F054FF-9704-4B40-9FBB-A9550487F43F}">
       <text>
         <r>
           <rPr>
@@ -2359,7 +2362,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K8" authorId="0" shapeId="0" xr:uid="{60D5E2AA-3307-45F2-BDA9-47885198D19C}">
+    <comment ref="K8" authorId="0" shapeId="0" xr:uid="{6D75887A-C854-4259-AD4B-A62AA314F634}">
       <text>
         <r>
           <rPr>
@@ -2384,7 +2387,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{DDD3D575-C916-482E-B4B0-6C5F0462B00C}">
+    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{A16FB699-D3F4-4769-A3F5-56387F0EA4A3}">
       <text>
         <r>
           <rPr>
@@ -2419,7 +2422,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{EFAB99CE-5455-4F45-861E-9FE87C5C23D9}">
+    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{4B24683D-741B-4FFB-9E78-473C3142B5AF}">
       <text>
         <r>
           <rPr>
@@ -2444,7 +2447,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N8" authorId="0" shapeId="0" xr:uid="{BDF1E066-2279-46D1-ADF8-9052965AFE99}">
+    <comment ref="N8" authorId="0" shapeId="0" xr:uid="{10DF7389-214B-4F8B-B09B-42CA9D647A9D}">
       <text>
         <r>
           <rPr>
@@ -2468,7 +2471,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{0667F70D-B9ED-455B-A3BF-F6CC969BF2A1}">
+    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{E8571940-7A3C-487B-B8D0-79C4E3809D32}">
       <text>
         <r>
           <rPr>
@@ -2492,7 +2495,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{37E7D73C-72A8-4E95-82E3-21DD7F5CBEDA}">
+    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{0C1FC1C6-080D-44E8-9056-0EDBF239A2AD}">
       <text>
         <r>
           <rPr>
@@ -2515,7 +2518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{82A41768-28B3-48AB-90C5-A130CD9405EE}">
+    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{BF3C6F3C-9B50-498B-AF64-8C7B5F3AFC84}">
       <text>
         <r>
           <rPr>
@@ -2540,7 +2543,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{D036B795-F392-4A69-8D2B-C56C34450D79}">
+    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{B99C26EC-A7F5-4C98-85B0-D49654BF7A88}">
       <text>
         <r>
           <rPr>
@@ -2565,7 +2568,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{244E7A6E-7E57-48B5-AFBB-9E0329E5751A}">
+    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{E5C8033C-33F3-42E5-AA93-85535EA5782D}">
       <text>
         <r>
           <rPr>
@@ -2590,7 +2593,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{EA347EA1-3650-45C5-B18F-06097545C4D7}">
+    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{741730A0-55A5-4871-BFBC-AB85A69D2328}">
       <text>
         <r>
           <rPr>
@@ -2615,22 +2618,22 @@
         </r>
       </text>
     </comment>
-    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{987E1BAD-D832-4C62-ADF2-882225DFD445}">
+    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{1934B238-DD2F-4F8D-B5C2-605CB128FDA2}">
       <text/>
     </comment>
-    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{1E99B71A-1396-45B6-8D1C-FD826E85C181}">
+    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{F4324D76-DB18-4EA0-80C8-A5D41BF6430C}">
       <text/>
     </comment>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{D79FCF0C-D9F7-4534-960B-5826726799F1}">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{536F1F09-498C-4CD7-ACBD-973ABAFC45A8}">
       <text/>
     </comment>
-    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{08341A5E-96EB-4A42-B54B-FD3C3C36A118}">
+    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{7873D641-930B-412C-99EB-ACCE1B6903BA}">
       <text/>
     </comment>
-    <comment ref="L11" authorId="0" shapeId="0" xr:uid="{5F809FE9-1E83-4056-87B5-937B0F4C7C39}">
+    <comment ref="L11" authorId="0" shapeId="0" xr:uid="{CA592E41-51E8-4A0A-A770-D6BFB2D6692B}">
       <text/>
     </comment>
-    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{E79CF467-5307-48F1-9905-41515476A1D2}">
+    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{CE60AD7E-E8F4-4842-AAC7-1183432930D8}">
       <text>
         <r>
           <rPr>
@@ -2655,7 +2658,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N11" authorId="0" shapeId="0" xr:uid="{882F896D-5362-4461-895E-398CE20942BA}">
+    <comment ref="N11" authorId="0" shapeId="0" xr:uid="{E3551E66-1E47-46B4-8C3E-FAAF631527DD}">
       <text>
         <r>
           <rPr>
@@ -2679,30 +2682,30 @@
         </r>
       </text>
     </comment>
-    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{98A4CDCA-9C19-4CF5-9BE3-C761B24CF66C}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Aullido de Belknapius: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>La criatura aulla, todas las criaturas en un radio de 10 metros deben hacer una tirada de RESI vs INT del taumaturgo. Aquellos que fallen quedan paralizados durante 3 turnos o hasta recibir daño. 2 RES, 2 maná.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C14" authorId="0" shapeId="0" xr:uid="{A313669A-A0C3-452A-A79B-5CA2B06BA2D8}">
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{C681949D-9CB6-4360-B779-65EF9A82937B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">El Llamado de los Cadáveres: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Puedes levantar no-muertos a partir de cadáveres que se encuentren hasta 20 metros a tu alrededor, alza un máximo de 1d4+1d4 por cada 2 niveles. 3 de maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C14" authorId="0" shapeId="0" xr:uid="{B29B81D5-43CE-4EB9-84AE-47190CBC12B7}">
       <text>
         <r>
           <rPr>
@@ -2725,7 +2728,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{8A63D1CC-645F-4F35-A773-56FEDE7F7713}">
+    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{F6D20034-E09F-4D0F-B6A1-4AAC6705055D}">
       <text>
         <r>
           <rPr>
@@ -2748,7 +2751,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{F824C8F3-0D18-42BB-9D0E-89CBF2836B6C}">
+    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{465474A4-F5F6-41E3-8BEB-C090E0C03CE2}">
       <text>
         <r>
           <rPr>
@@ -2773,7 +2776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{9D0D5A21-E169-47E5-BC79-771FFC0CBFAD}">
+    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{9B9DF6E8-09FF-4CFB-96E4-FEC3B01C9263}">
       <text>
         <r>
           <rPr>
@@ -2798,7 +2801,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{0160378A-A362-43C7-A4C0-A5BE0F4583C8}">
+    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{C20B36D6-BE34-42EA-869F-B4A5D2B4F87A}">
       <text>
         <r>
           <rPr>
@@ -2823,7 +2826,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{EDB90EE3-ED48-4DAD-BDCA-21E1A7A1B9F3}">
+    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{85A181E2-BDCF-4871-A39F-746AF155793A}">
       <text>
         <r>
           <rPr>
@@ -2848,7 +2851,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{68FD1320-874B-485E-A19B-F406C48AD807}">
+    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{2DE3F587-72EF-415B-A1C7-AAEDFBB30E82}">
       <text>
         <r>
           <rPr>
@@ -2873,7 +2876,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{683F0516-91BA-40A2-ACE2-40C7DE6D38E6}">
+    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{EDDBC006-AD5E-4397-9846-83DCB0FA70C2}">
       <text>
         <r>
           <rPr>
@@ -2898,7 +2901,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{EFA26501-8838-4A16-A3F4-854F24D7673A}">
+    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{50A10281-E822-4DCB-9087-F29592987F0F}">
       <text>
         <r>
           <rPr>
@@ -2923,7 +2926,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L14" authorId="0" shapeId="0" xr:uid="{32C23DB6-F3F1-4574-A0CA-60DFA43EF19B}">
+    <comment ref="L14" authorId="0" shapeId="0" xr:uid="{9F3F8902-AD57-461E-9AD3-D57079E82899}">
       <text>
         <r>
           <rPr>
@@ -2948,7 +2951,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M14" authorId="0" shapeId="0" xr:uid="{39974B88-0BA9-4B95-AAD9-485DC390F55C}">
+    <comment ref="M14" authorId="0" shapeId="0" xr:uid="{3B9B4BD1-7ADC-42DD-94BD-A5A6F4D898FC}">
       <text>
         <r>
           <rPr>
@@ -2973,7 +2976,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N14" authorId="0" shapeId="0" xr:uid="{66EE5C46-D47E-4273-9C07-1F2CC478C443}">
+    <comment ref="N14" authorId="0" shapeId="0" xr:uid="{B417D6EC-DA7B-477E-AC62-A5FA7A90AFF5}">
       <text>
         <r>
           <rPr>
@@ -3008,7 +3011,53 @@
     <author>Lenovo</author>
   </authors>
   <commentList>
-    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{6B03402A-F41F-4C7D-A6C3-49CB44A870A0}">
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{C7064E69-F89D-4397-AF2A-4022D65CFC09}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Posesión Infernal: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">La criatura realiza un ataque cuerpo a cuerpo que no produce daño pero intenta introducir su materia nubosa dentro de una criatura que no sea constructo, ignoto, celestial o arcano y controlarlo. Para que sea efectivo además de que la chance cuerpo a cuerpo sea exitosa, debe hacer tiradas d20 de inteligencia como parte de la misma acción principal, debe superar los puntos de vida actuales y los puntos de resilencia del objetivo sumados, si acumula tres fallos fallará en la posesión, si acumula tres éxitos el infernal se introduce completamente dentro de su víctima, esta convulsiona brevemente durante unos segundos y el infernal toma total control del cuerpo de la criatura y se vuelven una sola unidad, las estadísticas de FZA, AGI y CON son las de la víctima y CAR, INT y SAB del infernal. El objetivo no esta muerto, pero su consciencia se encuentra dormida, el infernal adopta la clase de este, añadiendo el tipo ignoto a los tipos que ya tiene y la inscripción "poseído/a" despues del nombre. 3 RES. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{55A8DA2F-4870-4E20-8F41-AB141DE2BB42}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Baba Cegadora: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Ataque a distancia, la criatura lanza un escupitajo a un punto que pueda ver a 15 metros máximo de él, si el objetivo es otra criatura lo dirige directamente a los ojos. Si el ataque es exitoso el objetivo debe superar una tirada de salvación de Destreza CD 13 para no quedar cegadas hasta el final del siguiente turno del lanzador. 2 Res.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{FB95730E-D979-40CB-A11B-1E95813039DA}">
       <text>
         <r>
           <rPr>
@@ -3018,7 +3067,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Inmunidad Elemental: </t>
+          <t xml:space="preserve">Profanar Vida: </t>
         </r>
         <r>
           <rPr>
@@ -3027,57 +3076,11 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>(Pasivo) La criatura es inmune y no queda bajo los efectos de aturdir, envenenado, dormir y desangrar. También son inmunes a encantamientos y efectos que le pongan bajo el control de otra criatura.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{7E60D3AB-C760-4280-9B0A-8D7413451790}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Baba Cegadora: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Ataque a distancia, la criatura lanza un escupitajo a un punto que pueda ver a 15 metros máximo de él, si el objetivo es otra criatura lo dirige directamente a los ojos. Si el ataque es exitoso el objetivo debe superar una tirada de salvación de Destreza CD 13 para no quedar cegadas hasta el final del siguiente turno del lanzador. 2 Res.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{514A0B4A-3DAA-4B6F-BC1E-EBCD7806A80A}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Profanar Vida: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
           <t>(Conjuro) Extiende una extremidad hacia un objetivo y lanza un haz de luz oscura inmaterial (no puede ser bloqueado con elementos normales). Si golpea exitosamente al objetivo le hace daño de conjuro directo y ahora el taumaturgo puede dirigir esa misma cantidad de puntos hacia un cádaver que se encuentre a unos 15 metros de radio máximo del objetivo y al alcance de su vista. Éste es reanimado bajo el control del lanzador y se cura tantos puntos de vida como daño haya hecho al objetivo. 5 maná.</t>
         </r>
       </text>
     </comment>
-    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{AAA7A7B9-A8E7-4051-933F-7B6F65E6C047}">
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{46E47B66-CDE4-4E74-AA2A-16DE7A9A1D5F}">
       <text>
         <r>
           <rPr>
@@ -3102,7 +3105,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{E0749C12-51AC-4B06-9764-E2607697B425}">
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{22542D72-98E4-4CB8-BEE3-A5C38C06008B}">
       <text>
         <r>
           <rPr>
@@ -3127,7 +3130,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{7B2BC444-4682-4564-A136-7407DDC6B687}">
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{D3DC91B1-ADBB-47B4-8399-986C8A6E91F2}">
       <text>
         <r>
           <rPr>
@@ -3152,7 +3155,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{AB8B2126-F7C0-4489-A59A-43CD7E4D50AF}">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{2FA71643-9FF5-42FD-9DB5-DEC155F493EE}">
       <text>
         <r>
           <rPr>
@@ -3177,7 +3180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{9D5B7D38-85DA-46F8-895A-BB2A26316C50}">
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{B725D93C-9DC4-4A1F-AE39-5A05C638ED84}">
       <text>
         <r>
           <rPr>
@@ -3203,7 +3206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{46387788-5CE2-4245-9CD3-263E27165284}">
+    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{30537D8E-285F-4A1A-A94B-A6D03D89B1EC}">
       <text>
         <r>
           <rPr>
@@ -3228,7 +3231,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{807E000C-C39D-4519-BE18-E4FB05B41128}">
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{1E2C7054-9728-464F-9829-A8996FFDC9B7}">
       <text>
         <r>
           <rPr>
@@ -3253,7 +3256,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{EACC5BCD-8600-47DE-8B01-D20E71855D7B}">
+    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{97C05670-C8F3-438F-9622-998DC8BC8BE7}">
       <text>
         <r>
           <rPr>
@@ -3278,7 +3281,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{1BA987BE-F9C9-4723-953D-5651933E46F2}">
+    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{B174C16E-E14D-4FA8-88E3-82CC8395D8CD}">
       <text>
         <r>
           <rPr>
@@ -3303,7 +3306,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{BE1EC722-278E-43C8-B182-A2038F8644D5}">
+    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{F55D79A1-6E9B-42A7-B56A-6EC79C20D044}">
       <text>
         <r>
           <rPr>
@@ -3327,53 +3330,53 @@
         </r>
       </text>
     </comment>
-    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{844140F1-8348-44B2-9304-8275F7738CF5}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Atrapacráneos: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">La criatura realiza un ataque cuerpo a cuerpo que no produce daño pero intenta aferrarse a la cabeza de un humanoide y envolverla por completo con su boca. Para que sea efectivo además de que la chance cuerpo a cuerpo sea exitosa, debe hacer tiradas d20 de inteligencia como parte de la misma acción principal, debe superar los puntos de vida actuales y los puntos de resilencia del objetivo sumados, si acumula tres fallos se soltará sin poder atrapar a su objetivo, si acumula tres éxitos el ignoto engulle completamente la cabeza de la víctima sujetándose con la dentición que posee dentro de su cuerpo desde la abertura que se encuentra entre los tentáculos, la víctima convulsiona brevemente durante unos segundos y el ignoto toma total control de el cuerpo de su víctima y se vuelven una sola unidad, las estadísticas de FZA, AGI y CON son las de la víctima y CAR, INT y SAB del ignoto. El objetivo no esta muerto, pero su consciencia se encuentra dormida, el ignoto tiene acceso a todas las memorias y conocimientos del objetivo, adopta la clase de este y la unidad pasa a ser un "coronado", añadiendo el tipo ignoto a los que ya tiene. 3 RES. </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{BF77D629-3063-441A-8803-22D885634469}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Necrovida: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Encantamiento) Selecciona un objetivo al alcance de la vista, este debe realizar una tirada de su CON vs tu INT, si falla añade el tipo No-Muerto a los tipos que ya tiene y se convierte en uno durante 1d6 turnos +1d4 por cada 5 niveles. Mientras esta criatura es un no-muerto tienes control total de ella. 6 de maná.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{DAA22EF5-697C-441A-ADA8-C755FDFD85F5}">
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{83D8ABA7-05CF-4D7F-AE7D-CF5D2980DA10}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Materia Esquiva: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Pasivo) La consistencia de la criatura oscila entre los estados sólido y gaseoso, por lo cual el daño físico y elemental no le afecta totalmente, sus resistencias naturales son 11, 8, 14, 9, 6, 5.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{C66F9D7A-72A8-4E27-903D-8AC267EB767D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Piel del Inframundo: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Pasivo) Las defensas naturales de la criatura son 10, 12, 8, 24, 18, 9.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{8FBA1150-FB53-4226-80FB-92936C737BB8}">
       <text>
         <r>
           <rPr>
@@ -3398,7 +3401,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{9D05831C-0170-4B78-992F-6511F997760E}">
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{928F1912-4013-46B2-85EF-1B7E12A192B9}">
       <text>
         <r>
           <rPr>
@@ -3423,7 +3426,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{F0A24FAE-1973-46FC-81C6-2FE36E19F27B}">
+    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{B64DDE96-3F21-4346-B090-7590170B3729}">
       <text>
         <r>
           <rPr>
@@ -3448,7 +3451,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{42EC7CF8-A943-4B98-8975-AB6B78FAD71D}">
+    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{60670469-0035-445E-8723-E716D5308A33}">
       <text>
         <r>
           <rPr>
@@ -3473,7 +3476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{B84DAA54-7E2E-450E-89D1-9751869FF862}">
+    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{02489D7C-4108-47E1-A81D-75AA18070D2A}">
       <text>
         <r>
           <rPr>
@@ -3498,7 +3501,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{F67D0006-84B9-431A-85C7-950C7F55AB7B}">
+    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{4852E822-8987-479D-AEDB-72C5DC7FDE24}">
       <text>
         <r>
           <rPr>
@@ -3523,7 +3526,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J5" authorId="0" shapeId="0" xr:uid="{1B5121D2-D10C-4DC7-8CEE-D2E7625AAADE}">
+    <comment ref="J5" authorId="0" shapeId="0" xr:uid="{B2E84B09-CAF5-4FFF-A744-33B13259AD69}">
       <text>
         <r>
           <rPr>
@@ -3549,7 +3552,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K5" authorId="0" shapeId="0" xr:uid="{84B54DC6-CA74-49AD-A407-AC5C19626AE9}">
+    <comment ref="K5" authorId="0" shapeId="0" xr:uid="{ACDCA6D2-8A0E-45B7-8527-74837936443C}">
       <text>
         <r>
           <rPr>
@@ -3575,7 +3578,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L5" authorId="0" shapeId="0" xr:uid="{C75A7248-4130-4ECA-92EB-85FD4B13756C}">
+    <comment ref="L5" authorId="0" shapeId="0" xr:uid="{CFE3E9DE-2A18-4A6F-8AB0-E89B97CD5C82}">
       <text>
         <r>
           <rPr>
@@ -3600,7 +3603,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M5" authorId="0" shapeId="0" xr:uid="{7B61DBA9-CAA7-4954-9EA0-B924E0A71A05}">
+    <comment ref="M5" authorId="0" shapeId="0" xr:uid="{90CC3AA6-DDFB-46AF-ACB1-1E573C501B40}">
       <text>
         <r>
           <rPr>
@@ -3625,7 +3628,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N5" authorId="0" shapeId="0" xr:uid="{E7E8D2ED-49EB-409A-A75A-3058DB3E7872}">
+    <comment ref="N5" authorId="0" shapeId="0" xr:uid="{3FB96D09-04B5-4BFE-9905-5B7CC59CEE92}">
       <text>
         <r>
           <rPr>
@@ -3649,7 +3652,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{506CA7C7-AD53-408E-9998-6DDF3F1544E9}">
+    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{BD65E44B-A74C-4305-BE10-2F4AB954BD40}">
       <text>
         <r>
           <rPr>
@@ -3659,7 +3662,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Materia Paradójica: </t>
+          <t xml:space="preserve">Ataque con Garras: </t>
         </r>
         <r>
           <rPr>
@@ -3668,103 +3671,104 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>(Pasivo) El ignoto posee una configuración material particular que le hace resistente. Sus defensas naturales son 18, 32, 27, 33, 38, 19.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{375AC01E-951E-48A8-A1C1-24C2B9C9CF5E}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Masa Gelatinosa: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Pasivo) La criatura está hecha de un material blando y viscoso que le provee cierta protección. Sus defensas naturales son 14, 26, 16, 15, 20, 7.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{EC6226E2-2E54-4C65-A9AA-69E3A03C6F22}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Consistencia Gelatinosa: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Pasivo) La criatura no tiene una forma completamente sólida por lo que los ataques físicos le hacen muy poco daño, siendo siempre 1, sin importar sus defensas. Sus defensas naturales son de 50, 50, 50, 18, 21, 8. La criatura tampoco puede realizar ataques físicos comunes. Si se le atacan con armas arrojadizas o proyectiles estos quedan dentro de su cuerpo y en 3d4 turnos se desintegrará por completo.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{88847AF8-8FA0-4062-AC6F-C23CA79B100D}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Materia Foránea: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Pasivo) Cada vez que la criatura es hecha objetivo particular de otra con intenciones perniciosas (daño, maldición, etc.) esta última pierde 1d4 puntos de cordura.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{A4DFADF4-14CE-4F05-8A6B-09CBCCAD2D0C}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Piel Pseudoescamoide: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Pasivo) La criatura tiene la piel cubierta por placas de costras endurecidas similares a escamas. Sus defensas naturales son 28, 19, 11, 32, 41, 5.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{441E9ED1-B237-4DD7-8D10-769320AFBEEF}">
+          <t>La criatura puede atacar en un turno tantas veces como extremidades con garras tenga con un mínimo de 1. Si al menos uno de los ataques es efectivo el objetivo realiza una tirada d20 de su CON vs la DES del atacante, si falla se le aplica un sangrado de 1d4 por 2 turnos +1 turno por cada 5 niveles.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{589C72F8-8CA0-4C38-B69B-49333637C527}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Mordida Fantasmal: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Ataque cuerpo a cuerpo con un bonus -2 a las defensas del objetivo -1 por cada 4 niveles. Hace daño perforante. El objetivo debe hacer una tirada d20 de DES vs la DES del atacante, si falla el daño ignora las defensas de armadura.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{C5112136-BAF6-4452-99CC-2DE96F56FA3C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Estocada Sanguinaria: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>La criatura ataca a un objetivo con un apéndice punzante, tira chance cuerpo a cuerpo. Aumenta el daño 1d6 + 1d6 por cada 5 niveles, hace daño perforante. Si el daño es efectivo el objetivo realiza una tirada de CON vs DES del atacanti, si falla sangra 1d4 por 3 turnos +1d4 por cada 5 niveles. 1 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{DD6E6FBC-5BC9-4CF4-80FE-445FF748180D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Mordida Demoníaca: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Ataque cuerpo a cuerpo en el que la criatura ataca violentamente con sus fauces al objetivo, hace daño perforante, el objetivo realiza una tirada d20 de CON vs la DES del atacante, si falla tiene un sangrado de 1d6 durante 5 turnos +1 por cada 5 niveles. 2 RES.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{4B13328E-2E30-434E-A45D-77DC5FC28107}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Embestida Brutal: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Ataque precedido por la acción de movimiento la cual debe recorrer mínimamente 1 metro. Hace daño base en contundente con un bonus de 1d6 +1d6 por cada 4 puntos de CON. Si el ataque impacta o es bloqueado por el objetivo este debe hacer una tirada de CON vs la FZA del atacante, si falla es desplazado 2 metros, +1 por cada 5 puntos de fuerza del atacante, y queda derribado y aturdido por 1 turno. 3 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{105A5A60-E262-4BB3-AFE6-D424DF476ACF}">
       <text>
         <r>
           <rPr>
@@ -3779,7 +3783,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{989E4EBC-4510-416F-AB61-6ED3377C288A}">
+    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{E2889347-ABFB-4EB9-93B5-ECADEACD7677}">
       <text>
         <r>
           <rPr>
@@ -3804,7 +3808,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{9BEF9792-1970-47F3-8160-E9099C25A454}">
+    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{4FB4D028-EA9E-4B16-A78A-F23934D3EBB1}">
       <text>
         <r>
           <rPr>
@@ -3818,7 +3822,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J8" authorId="0" shapeId="0" xr:uid="{AA115DAE-F4AA-42CA-AC3A-1B609AE2AFE8}">
+    <comment ref="J8" authorId="0" shapeId="0" xr:uid="{97275EF5-3FE9-4DE0-BB89-6724A505DE0F}">
       <text>
         <r>
           <rPr>
@@ -3844,7 +3848,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K8" authorId="0" shapeId="0" xr:uid="{E5CC5179-3210-4B35-B146-8D2650CAB8C4}">
+    <comment ref="K8" authorId="0" shapeId="0" xr:uid="{60D5E2AA-3307-45F2-BDA9-47885198D19C}">
       <text>
         <r>
           <rPr>
@@ -3869,7 +3873,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{BDEAF959-ABD4-44DC-B2B6-6DCEC8E2C8B0}">
+    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{DDD3D575-C916-482E-B4B0-6C5F0462B00C}">
       <text>
         <r>
           <rPr>
@@ -3904,7 +3908,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{B2A6558C-FE71-45C6-82D2-AE86F3628917}">
+    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{EFAB99CE-5455-4F45-861E-9FE87C5C23D9}">
       <text>
         <r>
           <rPr>
@@ -3929,7 +3933,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N8" authorId="0" shapeId="0" xr:uid="{8E366133-7EA2-4DE6-B3FD-AE2233B09F67}">
+    <comment ref="N8" authorId="0" shapeId="0" xr:uid="{BDF1E066-2279-46D1-ADF8-9052965AFE99}">
       <text>
         <r>
           <rPr>
@@ -3953,53 +3957,54 @@
         </r>
       </text>
     </comment>
-    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{7330AA39-F716-4782-8879-A3EF0DB887C7}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Surcar el Espacio: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Conjuro) Se ejecuta como acción de movimiento, no requiere tirada de chance. El taumaturgo se envuelve en energía psiquica y mueve su corporeidad, difuminándose parcialmente, un máximo de cuadros igual a sus puntos de INT dividido 2, redondeando hacia abajo. 1 de maná.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{79E38993-DD1E-4B0D-BD4E-55E2E152CD8C}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Levitar (Ignotos): </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>La criatura puede moverse desplazándose sin tocar el suelo hasta una altura máxima de unos 20 mts aprox y a una velocidad de 1 metro por cada 3 puntos de INT.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{67CCE25C-1727-4C77-A9CD-40EE59FB9539}">
+    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{0667F70D-B9ED-455B-A3BF-F6CC969BF2A1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Rastrear a los Pecadores: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">La criatura hace una tirada de SUP con CD 13, si es exitoso detecta la posición exacta de hasta 1 criatura, +1 por cada 4 niveles, de tipo ignoto o que entre sus habilidades cuente con al menos una de las escuelas de necromancia, demonología o profano o que haya atacado a la criatura o a su invocador en el pasado. La o las que se encuentren más cerca a él dentro de un radio de 500 metros. Una vez detectada tiene +1d4 de bonus a los daños que le inflinja, +1d4 por cada 4 niveles y el objetivo no puede ocultarse de la criatura ni siquiera por métodos mágicos como invisibilidad. 2 de maná.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{37E7D73C-72A8-4E95-82E3-21DD7F5CBEDA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Visión Espectral: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Pasivo) La criatura puede ver perfectamente en la oscuridad absoluta y puede ver a unidades invisibles sin problema.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{82A41768-28B3-48AB-90C5-A130CD9405EE}">
       <text>
         <r>
           <rPr>
@@ -4024,7 +4029,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{B34D338C-5F0E-4358-8B03-3E93911F75EA}">
+    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{D036B795-F392-4A69-8D2B-C56C34450D79}">
       <text>
         <r>
           <rPr>
@@ -4049,7 +4054,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{009C78DB-9608-436B-A61E-835541ED00FF}">
+    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{244E7A6E-7E57-48B5-AFBB-9E0329E5751A}">
       <text>
         <r>
           <rPr>
@@ -4074,7 +4079,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{91FC6631-1FFA-4BB6-B6A5-EB8376716D66}">
+    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{EA347EA1-3650-45C5-B18F-06097545C4D7}">
       <text>
         <r>
           <rPr>
@@ -4099,22 +4104,22 @@
         </r>
       </text>
     </comment>
-    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{0E25F7FE-8BAE-430C-B825-98F9ACE106B6}">
+    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{987E1BAD-D832-4C62-ADF2-882225DFD445}">
       <text/>
     </comment>
-    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{BEC0D9FB-5F95-4C19-8F50-AE69323C646E}">
+    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{1E99B71A-1396-45B6-8D1C-FD826E85C181}">
       <text/>
     </comment>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{A246D66B-1EB8-4361-8FDC-F8AD753930AA}">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{D79FCF0C-D9F7-4534-960B-5826726799F1}">
       <text/>
     </comment>
-    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{DB3558CC-D89A-487A-90A9-FDE37FCAD8E0}">
+    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{08341A5E-96EB-4A42-B54B-FD3C3C36A118}">
       <text/>
     </comment>
-    <comment ref="L11" authorId="0" shapeId="0" xr:uid="{5CA11CD8-2ECE-4F09-B82A-2790B8DDAA22}">
+    <comment ref="L11" authorId="0" shapeId="0" xr:uid="{5F809FE9-1E83-4056-87B5-937B0F4C7C39}">
       <text/>
     </comment>
-    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{A4F1BFA0-A23C-472B-BE5E-6EE4E87E0FF3}">
+    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{E79CF467-5307-48F1-9905-41515476A1D2}">
       <text>
         <r>
           <rPr>
@@ -4139,7 +4144,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N11" authorId="0" shapeId="0" xr:uid="{1ED944E3-70E5-418F-A642-9203A5122E09}">
+    <comment ref="N11" authorId="0" shapeId="0" xr:uid="{882F896D-5362-4461-895E-398CE20942BA}">
       <text>
         <r>
           <rPr>
@@ -4163,30 +4168,30 @@
         </r>
       </text>
     </comment>
-    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{5661295B-121D-4C72-9D46-E2DE6DB9F09D}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">El Llamado de los Cadáveres: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Puedes levantar no-muertos a partir de cadáveres que se encuentren hasta 20 metros a tu alrededor, alza un máximo de 1d4+1d4 por cada 2 niveles. 3 de maná.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C14" authorId="0" shapeId="0" xr:uid="{29EE3406-84E4-4FA9-BDB8-EE2E3B318A1D}">
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{98A4CDCA-9C19-4CF5-9BE3-C761B24CF66C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Aullido de Belknapius: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>La criatura aulla, todas las criaturas en un radio de 10 metros deben hacer una tirada de RESI vs INT del taumaturgo. Aquellos que fallen quedan paralizados durante 3 turnos o hasta recibir daño. 2 RES, 2 maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C14" authorId="0" shapeId="0" xr:uid="{A313669A-A0C3-452A-A79B-5CA2B06BA2D8}">
       <text>
         <r>
           <rPr>
@@ -4209,7 +4214,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{1EED3939-89F4-4299-8FEF-1BC0678FF667}">
+    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{8A63D1CC-645F-4F35-A773-56FEDE7F7713}">
       <text>
         <r>
           <rPr>
@@ -4232,7 +4237,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{FF2B2A4A-2BDA-4A46-BE9F-18CDCC15A5FC}">
+    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{F824C8F3-0D18-42BB-9D0E-89CBF2836B6C}">
       <text>
         <r>
           <rPr>
@@ -4257,7 +4262,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{2961B428-CD8B-41D0-B3EB-F3E5ABED3638}">
+    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{9D0D5A21-E169-47E5-BC79-771FFC0CBFAD}">
       <text>
         <r>
           <rPr>
@@ -4282,7 +4287,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{7E22656B-689E-4005-ABAD-EBBD6217DFC5}">
+    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{0160378A-A362-43C7-A4C0-A5BE0F4583C8}">
       <text>
         <r>
           <rPr>
@@ -4307,7 +4312,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{8EA6C68A-6B64-4947-B9DF-AF3CD5B3FE4E}">
+    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{EDB90EE3-ED48-4DAD-BDCA-21E1A7A1B9F3}">
       <text>
         <r>
           <rPr>
@@ -4332,7 +4337,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{90FDFBE4-0323-48C3-8FE0-51B61ADCE398}">
+    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{68FD1320-874B-485E-A19B-F406C48AD807}">
       <text>
         <r>
           <rPr>
@@ -4357,7 +4362,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{5F3A9382-6D62-46F2-AF0B-135A59780278}">
+    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{683F0516-91BA-40A2-ACE2-40C7DE6D38E6}">
       <text>
         <r>
           <rPr>
@@ -4382,7 +4387,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{4D04E8CF-8B43-4E49-8D40-2C9E3E6B889B}">
+    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{EFA26501-8838-4A16-A3F4-854F24D7673A}">
       <text>
         <r>
           <rPr>
@@ -4407,7 +4412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L14" authorId="0" shapeId="0" xr:uid="{AE3F402D-1E73-4861-B10D-8AF66FFC4585}">
+    <comment ref="L14" authorId="0" shapeId="0" xr:uid="{32C23DB6-F3F1-4574-A0CA-60DFA43EF19B}">
       <text>
         <r>
           <rPr>
@@ -4432,7 +4437,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M14" authorId="0" shapeId="0" xr:uid="{2E2E44C4-383E-4DE6-A8E4-62A39511E4A2}">
+    <comment ref="M14" authorId="0" shapeId="0" xr:uid="{39974B88-0BA9-4B95-AAD9-485DC390F55C}">
       <text>
         <r>
           <rPr>
@@ -4457,7 +4462,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N14" authorId="0" shapeId="0" xr:uid="{41D06D88-D07C-44CF-BF98-D878211DC06B}">
+    <comment ref="N14" authorId="0" shapeId="0" xr:uid="{66EE5C46-D47E-4273-9C07-1F2CC478C443}">
       <text>
         <r>
           <rPr>
@@ -4492,7 +4497,7 @@
     <author>Lenovo</author>
   </authors>
   <commentList>
-    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{6C70779B-740F-4BE3-84BD-558B467D6848}">
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{6B03402A-F41F-4C7D-A6C3-49CB44A870A0}">
       <text>
         <r>
           <rPr>
@@ -4502,7 +4507,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Impulso: </t>
+          <t xml:space="preserve">Inmunidad Elemental: </t>
         </r>
         <r>
           <rPr>
@@ -4511,34 +4516,34 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Se apoya fuertemente en sus piernas para aumentar 2 metros sus salto o desplazamiento +1 metro por cada 4 niveles. Se usa como acción de movimiento. 3 RES.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{0479CB64-90BC-4D52-BD47-1EAB1EB2A981}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Vuela: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Pasivo)La criatura puede remontar vuelo utilizando alas o apéndices similares moviéndose tanta distancia como le permita su estadística de movimiento.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{D5A4CFAD-A461-4D93-AD6A-06AB44708DBC}">
+          <t>(Pasivo) La criatura es inmune y no queda bajo los efectos de aturdir, envenenado, dormir y desangrar. También son inmunes a encantamientos y efectos que le pongan bajo el control de otra criatura.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{7E60D3AB-C760-4280-9B0A-8D7413451790}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Baba Cegadora: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Ataque a distancia, la criatura lanza un escupitajo a un punto que pueda ver a 15 metros máximo de él, si el objetivo es otra criatura lo dirige directamente a los ojos. Si el ataque es exitoso el objetivo debe superar una tirada de salvación de Destreza CD 13 para no quedar cegadas hasta el final del siguiente turno del lanzador. 2 Res.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{514A0B4A-3DAA-4B6F-BC1E-EBCD7806A80A}">
       <text>
         <r>
           <rPr>
@@ -4548,7 +4553,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Montable: </t>
+          <t xml:space="preserve">Profanar Vida: </t>
         </r>
         <r>
           <rPr>
@@ -4557,61 +4562,713 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>(Pasivo) Esta criatura puede ser montada y dirigida por otra que cuente con el conocimiento de equitación.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{3E72F925-3B9A-4541-A24C-344C0436D937}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Agilidad Acuática: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>(Pasivo) Cuando la criatura se encuentra en el agua o bajo ella tiene un  bonus de agilidad igual a su nivel más su valor de fuerza.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{4254A6F7-B683-4049-B376-932F68CE2E47}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Viajero Incansable: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>(Pasivo) Bonus +8 de RES +4 por cada 4 niveles.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{26B59A2D-8524-428B-9F01-74B0FFC94BF9}">
+          <t>(Conjuro) Extiende una extremidad hacia un objetivo y lanza un haz de luz oscura inmaterial (no puede ser bloqueado con elementos normales). Si golpea exitosamente al objetivo le hace daño de conjuro directo y ahora el taumaturgo puede dirigir esa misma cantidad de puntos hacia un cádaver que se encuentre a unos 15 metros de radio máximo del objetivo y al alcance de su vista. Éste es reanimado bajo el control del lanzador y se cura tantos puntos de vida como daño haya hecho al objetivo. 5 maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{AAA7A7B9-A8E7-4051-933F-7B6F65E6C047}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Espinas Corruptas: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Ataque a distancia que lanza una serie de púas sólidas del cuerpo de la criatura a un objetivo, hace daño a distancia +1d6 por cada 4 niveles de la criatura. Daña también la cordura, 3 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{E0749C12-51AC-4B06-9764-E2607697B425}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Vómito Corrosivo: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Ataque a distancia donde la criatura lanza ácidos orgánicos a un objetivo que se encuentre a un máximo de 6 metros de distancia, si es efectivo hace daño similar al de fuego, por lo que se descuenta de esta defensa, si el objetivo falla una tirada de DES de 12 el daño ignora la armadura. Puede bloquearse con escudo, pero el defensor hace una tirada de DES de CD9, si falla el escudo se deshace por el ácido y queda inutilizado. 2 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{7B2BC444-4682-4564-A136-7407DDC6B687}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Atrapar y Digerir: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Ataque que se realiza en movimiento ocupando el mismo cuadro del objetivo para cubrirlo con la masa corporal y devorarlo. Puede ser bloqueado lo cual, si es exitoso, evita que la criatura se mueva. Si es exitoso no produce daño, pero el objetivo queda atrapado dentro de la criatura. En cada uno de sus turnos la víctima puede hacer una tirada de FZA vs CON de la criatura para intentar safarse y salir del cuadro que ocupa la criatura. En cada uno de los turnos de la criatura la víctima atrapada recibe 1d6 de daño directo +1d6 por cada 4 niveles y permanece dentro de ella por más que se mueva.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{AB8B2126-F7C0-4489-A59A-43CD7E4D50AF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Mordida Profana: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>La criatura ataca con los dientes o con alguna parte de su cuerpo similar a una boca dentada y hace daño base en perforante al objetivo. Si este recibe daño efectivamente hace una tirada de CON con CD de 12, si falla contrae la enfermedad "Peste Abismal", al cabo de 1d6 turnos comienza a afectarle, tiene desventaja para lanzar conjuros y encantamientos, tiene una penalización de 2d6 a INT y 2d8 a FZA, +1d6 por cada 4 niveles, puede sufrir alucinaciones y pierde 1d4 de cordura en cada turno. 3 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{9D5B7D38-85DA-46F8-895A-BB2A26316C50}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Ataque Lacerante: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Ataque cuerpo a cuerpo en el que la criatura utiliza sus extremidades o apéndices como látigos y golpea con ellos a un objetivo 1d4 veces +1d4 por cada 3 niveles, hace daño cortante.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{46387788-5CE2-4245-9CD3-263E27165284}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Onda Psíquica: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Conjuro) Crea una deformación en el espacio de forma esferoidal delante de él y la arroja hacia un objetivo violentamente. Hace daño de conjuro en contundente, puede bloquearse. Si golpea exitosamente el objetivo debe hacer una tirada de CON vs tu INT, si falla es derribado. 1 Maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{807E000C-C39D-4519-BE18-E4FB05B41128}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Rayos Abisales: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Conjuro) La criatura proyecta un rayo de energía abisal que, con la fricción con las partículas de el plano mortal, generan altas temperaturas capaz de producir quemaduras e incendio, lanza hasta 6 rayos y en una sola tirada de chance de conjuro, puede distribuir cada uno como quiera en hasta 6 enemigos. 7 Maná</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{EACC5BCD-8600-47DE-8B01-D20E71855D7B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Ondas Decoherentes: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Conjuro) La criatura suelta unas ondas de energía abismal por la boca a un objetivo que pueda ver, hace daño de conjuro y reduce 1d8 todas las estadísticas principales durante 3 turnos +1d4 por cada 6 niveles del lanzador. Puede bloquearse con escudo. 8 de maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{1BA987BE-F9C9-4723-953D-5651933E46F2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Veneno 1: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Lanza un ataque común cuerpo a cuerpo realizado con el órgano en el cual porta veneno haciendo el daño correspondente, luego realiza una tirada de DES vs la CON del objetivo, si es exitosa envenena y hace 1d4 de daño durante5 turnos +1 turno por cada 4 niveles. 1 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{BE1EC722-278E-43C8-B182-A2038F8644D5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Embestida con Cuernos: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Ataque que es precedido por un movimiento mínimo de 1 metro, aumenta el daño 1d4 por cada metro  recorrido en línea recta hasta tu objetivo y hace daño perforante golpeando con los cuernos. El objetivo realiza una TS de su CON vs tu FZA, si falla es derribado . 2 RES.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{844140F1-8348-44B2-9304-8275F7738CF5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Atrapacráneos: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">La criatura realiza un ataque cuerpo a cuerpo que no produce daño pero intenta aferrarse a la cabeza de un humanoide y envolverla por completo con su boca. Para que sea efectivo además de que la chance cuerpo a cuerpo sea exitosa, debe hacer tiradas d20 de inteligencia como parte de la misma acción principal, debe superar los puntos de vida actuales y los puntos de resilencia del objetivo sumados, si acumula tres fallos se soltará sin poder atrapar a su objetivo, si acumula tres éxitos el ignoto engulle completamente la cabeza de la víctima sujetándose con la dentición que posee dentro de su cuerpo desde la abertura que se encuentra entre los tentáculos, la víctima convulsiona brevemente durante unos segundos y el ignoto toma total control de el cuerpo de su víctima y se vuelven una sola unidad, las estadísticas de FZA, AGI y CON son las de la víctima y CAR, INT y SAB del ignoto. El objetivo no esta muerto, pero su consciencia se encuentra dormida, el ignoto tiene acceso a todas las memorias y conocimientos del objetivo, adopta la clase de este y la unidad pasa a ser un "coronado", añadiendo el tipo ignoto a los que ya tiene. 3 RES. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{BF77D629-3063-441A-8803-22D885634469}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Necrovida: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Encantamiento) Selecciona un objetivo al alcance de la vista, este debe realizar una tirada de su CON vs tu INT, si falla añade el tipo No-Muerto a los tipos que ya tiene y se convierte en uno durante 1d6 turnos +1d4 por cada 5 niveles. Mientras esta criatura es un no-muerto tienes control total de ella. 6 de maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{DAA22EF5-697C-441A-ADA8-C755FDFD85F5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Visión Ominosa: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Encantamiento) Esta habilidad no requiere tirada de chance. Utiliza tu acción principal para enfocar tu vista en un objetivo que también pueda verte, si este falla una tirada de DES vs tu INT pierde 1d6 puntos de cordura +1d4 por cada 4 niveles y queda cegado por 1d4 turnos.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{9D05831C-0170-4B78-992F-6511F997760E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Languidecencia Inducida: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Encantamiento) Mira fijamente a una criatura e intenta inducirla en un sopor somnífero, ésta hace una tirada de RESI vs tu CAR, si falla cae dormida por 1d4 turnos y tiene una penalización de RESI igual a tu daño de encantamiento. Los constructos, no-muertos e ignotos son inmunes a estos efectos. 6 de maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{F0A24FAE-1973-46FC-81C6-2FE36E19F27B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Perturbación: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Encantamiento) Lanza una onda psíquica a un objetivo que puedas ver, esta tiene una penalización de inteligencia de 1d8 + 1d4 por cada 5 niveles si falla una tirada de RESI vs la INT del taumaturgo y sufre de dolores que le impiden concentrarce y le causa desventaja en las tiradas de conjuro y hechizos. 3 de maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{42EC7CF8-A943-4B98-8975-AB6B78FAD71D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Ilusión Abismal: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Encantamiento) El taumaturgo solo puede lanzar este encantamiento a una unidad que haya le atacado, lanzado un hechizo o cualquier accion que haya hecho del lanzador un objetivo particular. Fija la vista en el objetivo el cual hace una TS de RESI vs tu INT, si falla tiene visiones de los abismos cercanos al oblivión y sufre de terror por 2d4 turnos + 1d4 por cada 6 niveles, también pierde tantos puntos de COR como daño de encantamiento tenga el lanzador. 7 de maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{B84DAA54-7E2E-450E-89D1-9751869FF862}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Pulso de Locura: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Conjuro) Suelta una onda de distorsión que afecta las mentes de todas las criaturas en un radio de 5 metros que no sean ignotos, no muertos, constructos o infernales deben hacer una TS de RESI vs tu INT, los que fallen pierden 1d4 puntos de cordura +1d4 por cada 3 niveles y quedan bajo los efectos de miedo durante 1 turno +1 por cada 4 niveles, los que sufran miedo hacen una nueva tirada exactamente igual, si fallan tienen, también, el efecto de aturdido por 1d4 turnos. 7 maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{F67D0006-84B9-431A-85C7-950C7F55AB7B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Disrupción: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(conjuro) Conjura un rayo de energía y lo lanza a un objetivo al alcance de la vista hasta 12 metros de distancia. Lanza 1d4, 1d6 o 1d8, a tu elección, haz ese número en daño eléctrico al objetivo, luego resta el número que dieron los dados a tu daño de conjuro y haz ese resultado a los puntos de maná del objetivo. Por cada 4 niveles puedes tirar un dado más del elegido si lo deseas. 3 maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J5" authorId="0" shapeId="0" xr:uid="{1B5121D2-D10C-4DC7-8CEE-D2E7625AAADE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Chillido Abisal: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>La criatura produce una poderosa y perturbadora onda de sonido. Todos los objetivos en 8 mts que no sean ignotos, no muertos, constructos, infernales o arcanos deben hacer una tirada de RESI o DES (para cubrirse los órganos auditivos), los que fallen sufren sordera y aturdimiento y no pueden entrar en concentración por 2 turnos y pierden 1d4 puntos de cordura en cada uno +1d4 por cada 4 niveles. No necesita tirada de chance. 
+3 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K5" authorId="0" shapeId="0" xr:uid="{84B54DC6-CA74-49AD-A407-AC5C19626AE9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Visión Inefable: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">(Pasivo) La sola visión de la criatura es incomprensible para los simples mortales. Cuando una criatura que no sea ignoto, elemental, bestia, no muerto, constructo, arcana o infernal dirige su atención viendo a la criatura, ya sea para comunicarse con ella o lanzar un hechizo o habilidad, pierde 1d8 puntos de cordura +1d8 por cada 5 niveles.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L5" authorId="0" shapeId="0" xr:uid="{C75A7248-4130-4ECA-92EB-85FD4B13756C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Control Mental (Ignotos): </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Encantamiento) Encanta a una criatura que no sea no-muerto, ignoto o constructo, esta realiza tres tiradas d20 de RESI vs tu INT, si falla dos de ellas el taumaturgo entra en concentración y en su turno controla completamente a la criatura encantada, ésta puede hacer en cada uno de sus turnos una tirada d20 de INT vs la INT del lanzador, si es exitosa se libra del control. 7 de maná, dura 5 turnos, luego de este plazo cuesta 1 de maná para mantener el control.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M5" authorId="0" shapeId="0" xr:uid="{7B61DBA9-CAA7-4954-9EA0-B924E0A71A05}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Rayo Confuso: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Conjuro) Conjura y lanza un rayo de energía a una criatura que no sea un constructo, si impacta esta hace una tirada de RESI vs tu CAR, si falla te verá como un aliado y a sus aliados como enemigos, en su próximos 2 turnos sentirá una gran ira hacia ellos y debe hacer todo a su alcance para atacarles con los medios que tenga disponibles, si no tiene aliados debe herirse a sí mismo. 4 de maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N5" authorId="0" shapeId="0" xr:uid="{E7E8D2ED-49EB-409A-A75A-3058DB3E7872}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Embestida con Cuernos: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Ataque que es precedido por un movimiento mínimo de 1 metro, aumenta el daño 1d4 por cada metro  recorrido en línea recta hasta tu objetivo y hace daño perforante golpeando con los cuernos. El objetivo realiza una TS de su CON vs tu FZA, si falla es derribado . 2 RES.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{506CA7C7-AD53-408E-9998-6DDF3F1544E9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Materia Paradójica: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Pasivo) El ignoto posee una configuración material particular que le hace resistente. Sus defensas naturales son 18, 32, 27, 33, 38, 19.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{375AC01E-951E-48A8-A1C1-24C2B9C9CF5E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Masa Gelatinosa: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Pasivo) La criatura está hecha de un material blando y viscoso que le provee cierta protección. Sus defensas naturales son 14, 26, 16, 15, 20, 7.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{EC6226E2-2E54-4C65-A9AA-69E3A03C6F22}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Consistencia Gelatinosa: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Pasivo) La criatura no tiene una forma completamente sólida por lo que los ataques físicos le hacen muy poco daño, siendo siempre 1, sin importar sus defensas. Sus defensas naturales son de 50, 50, 50, 18, 21, 8. La criatura tampoco puede realizar ataques físicos comunes. Si se le atacan con armas arrojadizas o proyectiles estos quedan dentro de su cuerpo y en 3d4 turnos se desintegrará por completo.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{88847AF8-8FA0-4062-AC6F-C23CA79B100D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Materia Foránea: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Pasivo) Cada vez que la criatura es hecha objetivo particular de otra con intenciones perniciosas (daño, maldición, etc.) esta última pierde 1d4 puntos de cordura.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{A4DFADF4-14CE-4F05-8A6B-09CBCCAD2D0C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Piel Pseudoescamoide: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Pasivo) La criatura tiene la piel cubierta por placas de costras endurecidas similares a escamas. Sus defensas naturales son 28, 19, 11, 32, 41, 5.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{441E9ED1-B237-4DD7-8D10-769320AFBEEF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{989E4EBC-4510-416F-AB61-6ED3377C288A}">
       <text>
         <r>
           <rPr>
@@ -4622,7 +5279,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>Reflejos de Alimaña:</t>
+          <t xml:space="preserve">Transmisor de Peste Infecciosa: </t>
         </r>
         <r>
           <rPr>
@@ -4632,636 +5289,30 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t xml:space="preserve"> (Pasivo) Tus tiradas de eludir tienen +8 y si son efectivas puedes utilizar 2 de RES para desplazarte un metro al eludir.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{AA49DE8C-E887-4CBC-B4F8-ED3111B6A86A}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Trepamuros: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>(Pasivo) La criatura puede utilizar los pequeños vellos de sus patas, extremidades o extensiones similares para aderirse a superficies como paredes y techos y moverse libremente por ellas como si andara normalmente en el suelo.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{C694EB33-B2E9-45CB-8EC2-C6F2A7D14AE2}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Surcar las Aguas: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Habilidad que se utiliza como acción de movimiento. Cuando la criatura está en un medio acuático puede acelerar y duplicar su velocidad máxima de movimiento durante ese turno. 2 RES.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{5507532E-DCFC-4973-AEDF-6F97EAAB9D34}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Unidad de Enjambre: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>(Pasivo) La unidad está compuesta por múltiples criaturas que se mueven y actúan juntas como una nube de enjambre, el hecho de que no sea una sola provee ciertas defensas físicas al grupo, aumentando sus resistencias naturales 9, 4, 13, 0, 0, 8. También puede ocupar y atravesar espacios ocupados por otra unidad y huecos pequeños en lugares como muros y puertas.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{58B440A6-5BF5-41FE-936D-05752BA8992C}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Hostigamiento de Enjambre: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Acción de movimiento donde el enjambre de criaturas ocupa el mismo espacio de movimiento que el objetivo, lo rodean en nube y se mueven con este si se mueve en cada turno. El objetivo tiene desventaja en sus ataques físicos y defensas. El atacante no necesita tiradas de chance de ataque cuerpo a cuerpo mientras esté en la posición de su objetivo pero solo puede atacarle a él. Ésta habilidad no necesita chance de tirada.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{4408EB69-0042-4B02-BCDF-B2084AD1961D}">
-      <text/>
-    </comment>
-    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{B942F10B-C607-492B-AB0B-86BBD185F98C}">
-      <text/>
-    </comment>
-    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{7ED212F6-84E3-4C2C-918B-28D2D102FAE9}">
-      <text/>
-    </comment>
-    <comment ref="O2" authorId="0" shapeId="0" xr:uid="{9BC69E51-9F30-46FC-9AB9-8DB69506E0C8}">
-      <text/>
-    </comment>
-    <comment ref="P2" authorId="0" shapeId="0" xr:uid="{E846C7CD-5982-4632-9EE8-FCDC4E694DD9}">
-      <text/>
-    </comment>
-    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{053DD034-35EC-4808-B88E-CDCA5FC3109E}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Vigilancia Rapaz: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Enfoca su visión en un objetivo como acción principal, durante 3 turnos no necesita chance de ataque contra esa criatura y obtiene crítico a partir de una tirada de 15. Si obtiene un resultado crítico añade 1d4 al daño +1d4 por cada 4 niveles.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{8B4CDBE7-AFB4-409F-96C1-616266BD0A5B}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Sentidos Felinos: (</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Pasivo) Tu visión en la oscuridad es casi perfecta, tus sentidos están tan desarrollados que no tienes desventaja para defenderte ataques por la espalda o de objetivos que estén oculto.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{9B0FC5DB-AB9E-41BF-97F3-77CFF33351D5}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Oido Sensible: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Pasivo) Tu sentido de la audición está muy desarrollado, tienes +8 en las tiradas de SUP que involucren el oído y puedes percibir sonidos de hasta aprox 30 metros a tu alrededor si no hay nada que los ocluse.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{54319BD4-2239-43AD-9A71-F1E8B19C5A18}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Olfato Sensible: (Pasivo) </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>La criatura tiene un desarrollado sentido del olfato. Puede rastrear criaturas, alimentos u otras cosas por su aroma si lo conoce de antemano, y percibir los olores en un radio de 25 mts aproximadamente para saber que hay en el entorno excepto que algo interfiera con los olores. Tienes un bonus +8 a las tiradas de supervivencia cuando son para rastrear a una criatura y utilizas el olfato.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{EC0782DB-18DA-4FEF-9634-8F63283A8075}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Piel Dura 1: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">(Pasivo) La piel de la criatura provee resistencias naturales de 4, 6, 2, 4, 4, 2.
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{B12C2BA3-8285-4BC4-9CB7-11EF99819FCA}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Plumaje Férreo: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">(Pasivo) El denso plumaje de la criatura otorga resistencias naturales de 8, 6, 5, 2, 8, 8.
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{1542328A-CD48-4BAE-943C-5EAA6EC30DEE}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Pelaje Recio: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>(Pasivo) El animal posee una gruesa piel y un pelaje con una densidad considerable que le proteje de los elemento aumentando sus defensas naturales 3, 3, 1, 8, 19, 12.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{39066C73-4046-4D77-B070-159F4C11522A}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Piel Dura 2: (Pasivo) </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>La piel escamosa y resistente de la criatura le provee defensas, sobre todo a los daños físicos, que mejoran sus resistencias naturales 8, 5, 6, 3, 1, 2.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J5" authorId="0" shapeId="0" xr:uid="{2933E82F-9CB1-4497-82E0-0813C0834396}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Metabolismo Subacuático: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>(Pasivo) La criatura puede permanecer debajo del agua conteniento la respiración por un máximo de hasta 24 hs.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K5" authorId="0" shapeId="0" xr:uid="{9DE2F7F9-FC61-4818-876C-E5096C466AF8}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Camuflaje: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>(pasivo) La criatura tiene una bonificación de +5 a la estadística de  SIG +1 por cada 4 niveles.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L5" authorId="0" shapeId="0" xr:uid="{BD7AD65F-097A-40CB-AB9F-3210FC06FBF2}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Visión Térmica (Bestias): </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>(Bestias) La criatura ve las marcas térmicas de las cosas, por lo que puede notar las cosas que emiten calor sin ningún problema. Puede también detectar a criaturas ocultas que emitan calor corporal.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M5" authorId="0" shapeId="0" xr:uid="{15A917B6-FACE-4026-8EB8-9DAC95146E47}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Ecolocación (Bestias): </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>(Pasivo) La criatura puede "ver" con sonido, emitiendo sonidos prácticamente inaudibles (si desea) de alta frecuencia que rebotan en objetos y crean imágenes acústicas en el cerebro, pudiendo prescindir de la vista cuando sea necesario, tiene un bonus +2 a percepción +2 cada 5 niveles.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N5" authorId="0" shapeId="0" xr:uid="{51A797BE-150E-456A-8713-E2C5F26FDF52}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Reflejos Ofídios: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>(Pasivo) La criatura posee gran gracilidad y precisión de movimientos. Tiene bonus +4 a al ataque cuerpo a cuerpo, +6 a eludir y +3 DES, +1 a cada bonus cada 5 niveles.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O5" authorId="0" shapeId="0" xr:uid="{D72548C4-A0AB-4F66-B586-55F397F9F247}">
-      <text/>
-    </comment>
-    <comment ref="P5" authorId="0" shapeId="0" xr:uid="{0B3F086E-8802-4233-8874-9683B5359CB2}">
-      <text/>
-    </comment>
-    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{9ACC628E-CDD3-4C5A-8DD4-C80F6C69F6C5}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Embestida con Astas: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Ataque que es precedido por un movimiento mínimo de 1 metro, aumenta el daño 1d6 por cada metro  recorrido en línea recta hasta tu objetivo y hace daño contundetnte golpeando con las astas de la cabeza. El objetivo realiza una TS de su CON vs tu FZA, si falla es derribado . 2 RES.2 RES.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{8FBBA04B-C343-497C-ACAC-B32084792D00}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Mordida Feroz: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Realiza una tirada de ataque de daño perforante mordiendo a un objetivo, si impacta exitosamente el objetivo hace una tirada de CON vs tu DES, si falla aplica un sangrado igual a 1d6 + 1d4 extra por cada 4 niveles durante 3 turnos. 1 RES.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{52F9D227-6B41-4974-A8D4-1AF220D7FAD3}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Mordida Destajadora: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Ataca a un objetivo cuerpo a cuerpo con una mordida, si es exitosa hace daño perforante, y si supera una tirada de destreza con CD 12 provoca un sangrado de 1d8 por tres turnos + 1 turno por cada 4 niveles de la criatura.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{60D91A50-E4E1-47CF-B2B4-5D85A3B23ACF}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Ataque a los Ojos: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Si el ataque impacta exitosamente, el objetivo queda cegado hasta el final de su siguiente turno, si es crítico dura dos turnos, 2 RES.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{EAD670DA-339A-4966-A180-79D9EC123BF2}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Arañazo: Realiza un ataque cuerpo a cuerpo utilizando las garras, hace daño cortante +1d4. Si impacta exitosamente el objetivo hace una tirada de CON vs tu DES, si falla le produces un sangrado que hace 1d4 + 1d4 por cada 4 niveles durante 2 turnos. </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{9210F280-B3F6-469B-9154-1FEBA73CC2BB}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Ataque en Picada: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Solo funciona si la criatura está volando y si se ejecuta luego de una acción de movimiento. Da un bonus +3 para la chance de ataque cuerpo a cuerpo y aumenta el daño 1d4 + 1d4 por cada 2 metros recorridos hasta el objetivo.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{FD8C5B84-666F-4BE3-A396-50E4E19FAFAA}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Mordida Apresante: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Ataque cuerpo a cuerpo en el que la criatura intenta atrapar fuertemente a un objetivo de una extremidad, hace daño contundente +1d10 en daño contundente, el objetivo hace una tirada de CON vs la FZA de la criatura atacante, si falla queda atrapada entre las fauces de este y queda con el estado de lisado afectanto la articulación apresada. En cada uno de los turnos del objetivo este puede intentar liberarse haciendo una tirada de FZA vs la Fza del atacante, en cada turno de el atacante este puede elegir realizar el daño de la habilidad nuevamente como acción principal. 3 RES.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{4EFAC017-6E12-4EC4-8C75-C16539BB0A2A}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Embestir (Bestias):</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve"> Ataque que es precedido por un movimiento mínimo de 1 metro, aumenta el daño 1d4 por cada metro  recorrido en línea recta hasta tu objetivo y hace daño contundetnte, el objetivo realiza una TS de su CON vs tu FZA, si falla es derribado . 2 RES.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J8" authorId="0" shapeId="0" xr:uid="{68ECB2AF-0C08-478A-BD7F-19C1110943E0}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
+          <t>Puede rastrear criaturas por su olor si lo conoce de antemano. Tienes un bonus +8 a las tiradas de supervivencia cuando son para rastrear a una criatura y utilizas el olfato o el oído.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{9BEF9792-1970-47F3-8160-E9099C25A454}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Embestir (Bestias): Ataque que es precedido por un movimiento mínimo de 1 metro, aumenta el daño 1d4 por cada metro  recorrido en línea recta hasta tu objetivo y hace daño contundetnte, el objetivo realiza una TS de su CON vs tu FZA, si falla es derribado . 2 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J8" authorId="0" shapeId="0" xr:uid="{AA115DAE-F4AA-42CA-AC3A-1B609AE2AFE8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
             <family val="2"/>
@@ -5271,7 +5322,7 @@
         </r>
         <r>
           <rPr>
-            <sz val="18"/>
+            <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
             <family val="2"/>
@@ -5280,6 +5331,56 @@
           <t xml:space="preserve">Lanza un poderoso ataque con las patas traseras y aumenta el daño 1d8 + 1d4 pr cada 4 niveles. Si el ataque es exitoso el objetivo debe hacer tres TS de su CON vs tu FZA, si falla la primera cae derribado, si falla la segunda es desplazado 2 mts hacia atras, si falla la tercera queda aturdido por 2 turnos. 4 RES.
 </t>
         </r>
+      </text>
+    </comment>
+    <comment ref="K8" authorId="0" shapeId="0" xr:uid="{E5CC5179-3210-4B35-B146-8D2650CAB8C4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Atrapar: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Realiza una tirada de ataque cuerpo a cuerpo contra un objetivo que esté al alcance de tus extremidades o cuerpo, si es exitosa no hace daño y el objetivo queda apresado en tu poder, con las extremidades superiores y inferiores inutilizadas, para safarse debe hacer una TS de FZA vs tu FZA como acción principal en su turno. 3 RES</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{BDEAF959-ABD4-44DC-B2B6-6DCEC8E2C8B0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Constricción: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Cuando tienes una criatura atrapada con tu cuerpo o extremidades puedes utilizar tu acción de movimiento para apretarla fuertemente, esta acción no tiene TS y hace tu daño cuerpo a cuerpo en contundente, daña también la resistencia del objetivo. 3 RES</t>
+        </r>
         <r>
           <rPr>
             <sz val="11"/>
@@ -5288,97 +5389,36 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K8" authorId="0" shapeId="0" xr:uid="{5CF43AD9-9604-435B-A6D9-DF69ACACB038}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="20"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Atrapar: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="20"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Realiza una tirada de ataque cuerpo a cuerpo contra un objetivo que esté al alcance de tus extremidades o cuerpo, si es exitosa no hace daño y el objetivo queda apresado en tu poder, con las extremidades superiores y inferiores inutilizadas, para safarse debe hacer una TS de FZA vs tu FZA como acción principal en su turno. 3 RES</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{432CEA68-1487-4940-A459-E1D8745EA479}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="20"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Constricción: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="20"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Cuando tienes una criatura atrapada con tu cuerpo o extremidades puedes utilizar tu acción de movimiento para apretarla fuertemente, esta acción no tiene TS y hace tu daño cuerpo a cuerpo en contundente, daña también la resistencia del objetivo. 3 RES</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
           <t>.</t>
         </r>
       </text>
     </comment>
-    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{D95B8ACC-920B-4A64-968D-E41813BB9C61}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Giro Mortal: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>No necesita chance de ataque. Es necesario que la criatura tenga al objetivo atrapado entre sus fauces. Gira sobre si mismo y hace daño contundente directamente, si realiza este ataque efectivamente durante dos o más turnos consecutivos a partir del segundo realiza una tirada de FZA vs CON del objetivo, si es exitoso dos veces seguida le arranca la extremidad en la que lo tiene atrapado y le produce un sangrado de 1d12 durante 10 turnos, 3 RES.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N8" authorId="0" shapeId="0" xr:uid="{01621E41-16A3-41FE-B520-347D09035EAC}">
+    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{B2A6558C-FE71-45C6-82D2-AE86F3628917}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Veneno 1: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Lanza un ataque común cuerpo a cuerpo realizado con el órgano en el cual porta veneno haciendo el daño correspondente, luego realiza una tirada de DES vs la CON del objetivo, si es exitosa envenena y hace 1d4 de daño durante5 turnos +1 turno por cada 4 niveles. 1 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N8" authorId="0" shapeId="0" xr:uid="{8E366133-7EA2-4DE6-B3FD-AE2233B09F67}">
       <text>
         <r>
           <rPr>
@@ -5402,183 +5442,108 @@
         </r>
       </text>
     </comment>
-    <comment ref="O8" authorId="0" shapeId="0" xr:uid="{B57CCE3A-CBD2-450F-8B68-3A5D4CFD4FF2}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Pisotón (Bestias): </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Habilidad de ataque cuerpo a cuerpo en la que la criatura intenta aplastar con su pata a una criatura cuya clasificación de tamaño sea inferior. Hace daño contundente de base +1d8 +1d6 por cada 5 puntos de FZA por sobre la CON del objetivo +1d6 por cada nivel de tamaño por encima del objetivo y derriba a este, quien luego hace una tirada de RESI vs FZA del atacante, si falla queda aturdido por 2 turnos. Solo puede ser bloqueado por escudo. Si el atacante lo desea, y el ataque es efectivo, puede moverse al cuadro del objetivo y mantener su pata sobre este para mantenerlo atrapado, en cada turno del atacante hace daño base contundente, en cada turno del objetivo este puede hacer una tirada de FZA vs CON del atacante para liberarse.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P8" authorId="0" shapeId="0" xr:uid="{F29A1B3D-7871-4EDE-88C3-533FC787DB76}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Mordida Carroñera: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>La criatura vive a base del consumo de carne como dieta principal. Puede utilizarlas en una mordida en ataque cuerpo a cuerpo, con su respectiva tirada de chance, hace daño base cortante +1d4, +1d4 por cada 4 niveles, y se cura VID y RES la mitad de los puntos de daño que haga siendo el mínimo 1 y redondeando hacia abajo.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q8" authorId="0" shapeId="0" xr:uid="{B5285EE7-F3FF-44E2-80CD-0B56040F4457}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Picadura Hematófaga: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Ataque cuerpo a cuerpo en el cual el atacante hace daño perforante y absorbe una cierta cantidad de sangre. Quita tantos puntos de RES como VIDA haya quitado y aumenta estos a la VIDA del atacante. </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{B1C35BED-8494-476B-BB74-593308B26769}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Grunido: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Haces una tirada de INT vs RESI del objetivo, si este falla queda asustado por1 turno +1 por cada 4 puntos de FZA.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{F909FA28-53B1-463B-BBDF-3B836856BC8A}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Graznido de Alerta: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Alerta a todos los enemigos cercanos en un radio de 30 metros, todos los aliados no tienen desventajas al ser atacados por la espalda o por unidades ocultas.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{C11A6A66-B051-4F54-A174-016C1E41BCB3}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Guardián: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Puede rastrear criaturas por su olor si lo conoce de antemano. Tienes un bonus +8 a las tiradas de supervivencia cuando son para rastrear a una criatura y utilizas el olfato o el oído.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{1931BF49-AD06-4957-927F-7A1E278AB06B}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Mensajero Animal: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>(Pasivo) Puede seguir y recordar rutas.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{84C2EABE-A96E-4BB1-A961-79BFF44216C8}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
+    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{7330AA39-F716-4782-8879-A3EF0DB887C7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Surcar el Espacio: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Conjuro) Se ejecuta como acción de movimiento, no requiere tirada de chance. El taumaturgo se envuelve en energía psiquica y mueve su corporeidad, difuminándose parcialmente, un máximo de cuadros igual a sus puntos de INT dividido 2, redondeando hacia abajo. 1 de maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{79E38993-DD1E-4B0D-BD4E-55E2E152CD8C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Levitar (Ignotos): </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>La criatura puede moverse desplazándose sin tocar el suelo hasta una altura máxima de unos 20 mts aprox y a una velocidad de 1 metro por cada 3 puntos de INT.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{67CCE25C-1727-4C77-A9CD-40EE59FB9539}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Desplazamiento Planar: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Conjuro) Como acción de movimiento el taumaturgo desterra por un instante su materia del plano en el que se encuentra a uno temporal y la regresa hasta 1 metro de distancia por cada 2 puntos de inteligencia posea. Puede atravesar espacios ocupados por otras criaturas durante su trayecto. 2 maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{B34D338C-5F0E-4358-8B03-3E93911F75EA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Anatomía de los Profundos: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Pasivo) La criatura puede moverse en entornos acuáticos con soltura, trasládándose el triple de rápido de lo que su velócidad de movimiento le permite.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{009C78DB-9608-436B-A61E-835541ED00FF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
             <family val="2"/>
@@ -5588,7 +5553,7 @@
         </r>
         <r>
           <rPr>
-            <sz val="18"/>
+            <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
             <family val="2"/>
@@ -5598,7 +5563,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{6848059F-15DE-49F4-A6D4-C49FD31B9BF7}">
+    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{91FC6631-1FFA-4BB6-B6A5-EB8376716D66}">
       <text>
         <r>
           <rPr>
@@ -5623,81 +5588,22 @@
         </r>
       </text>
     </comment>
-    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{B4FE115A-8F06-4ACE-8ABA-1DC7110D7C40}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Molestar y Perturbar: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">(Pasivo) Cuando la criatura está ocupando el mismo lugar que otra esta última tiene desventaja al realizar acciones que tengan como objetivo a otra criatura que no sea la que porta la habilidad, tampoco puede entrar en concentración. </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{DB87FC78-B3DA-4E70-879A-7C1C3AB94A68}">
+    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{0E25F7FE-8BAE-430C-B825-98F9ACE106B6}">
       <text/>
     </comment>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{9AA409D8-1F48-43CD-9362-45E8FB3F7E30}">
+    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{BEC0D9FB-5F95-4C19-8F50-AE69323C646E}">
       <text/>
     </comment>
-    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{11D589E4-07A2-45B9-925C-E806FF23824D}">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{A246D66B-1EB8-4361-8FDC-F8AD753930AA}">
       <text/>
     </comment>
-    <comment ref="L11" authorId="0" shapeId="0" xr:uid="{CFE920E3-F0EE-4CD3-A16F-17D6BB45398C}">
+    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{DB3558CC-D89A-487A-90A9-FDE37FCAD8E0}">
       <text/>
     </comment>
-    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{6E925165-6DDC-4A82-8DB3-C750D342974E}">
+    <comment ref="L11" authorId="0" shapeId="0" xr:uid="{5CA11CD8-2ECE-4F09-B82A-2790B8DDAA22}">
       <text/>
     </comment>
-    <comment ref="N11" authorId="0" shapeId="0" xr:uid="{81B5587D-C3EA-437A-A3FB-AC0214E9408D}">
-      <text/>
-    </comment>
-    <comment ref="O11" authorId="0" shapeId="0" xr:uid="{3D7FB5C6-2D8F-4AAF-8BDB-606AF97A2751}">
-      <text/>
-    </comment>
-    <comment ref="P11" authorId="0" shapeId="0" xr:uid="{8C8897CD-C875-4DBC-8F25-EC1031BA6A3B}">
-      <text/>
-    </comment>
-    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{EF850E00-659B-4047-A8D9-DBD9C6355512}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="20"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Transmisor de Peste Infecciosa: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="20"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Puede rastrear criaturas por su olor si lo conoce de antemano. Tienes un bonus +8 a las tiradas de supervivencia cuando son para rastrear a una criatura y utilizas el olfato o el oído.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C14" authorId="0" shapeId="0" xr:uid="{90F07E64-EDC6-4D03-B256-1D44FE5CBEAE}">
+    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{A4F1BFA0-A23C-472B-BE5E-6EE4E87E0FF3}">
       <text>
         <r>
           <rPr>
@@ -5722,110 +5628,348 @@
         </r>
       </text>
     </comment>
-    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{80985EDB-18D6-4997-A511-ACCA4964F04C}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Ácido Corrosivo: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>La criatura vomita un jugo estómacal extremadamente corrosivo, debe efectuar una tirada de chance de ataque a distancia. Puede bloquearse con escudo pero si impacta en este o si cae sobre una parte de la armadura (a criterio azaroso decisión del DM) el portador hace una tirada de DES con CD 14, si falla la pieza alcanzada puede dañarse y quedar inutilizada. Hace 1d8 de daño de fuego +1d6 por cada 4 niveles. 2 RES.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{257C9967-340B-4F16-8DD7-250D0EA9F134}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Ponzoña: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>La criatura pica con su aguijón o apéndice en punta con veneno haciendo la respectiva tirada cuerpo a cuerpo con un bonus +5 a la tirada de chance +1 por cada 3 niveles. Si el ataque es efectivo hace daño base en perforante y aplica una poderosa toxina que hace 1d4 -1  de daño, +1d4 por cada 4 niveles, durante 6 turnos, +1 por cada 4 niveles, provoca dolor por lo cual el objetivo no puede entrar en concentración y tiene -5 a las tiradas de chance de conjuros y encantamientos, +1 por cada 4 niveles. 1 RES.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{256EBAD5-3AA3-448B-96A3-16D016F0B14F}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Veneno 1: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Lanza un ataque común cuerpo a cuerpo realizado con el órgano en el cual porta veneno haciendo el daño correspondente, luego realiza una tirada de DES vs la CON del objetivo, si es exitosa envenena y hace 1d8 de daño durante 5 turnos +1 turno por cada 4 niveles. 1 RES.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{800013D1-AE8B-48C5-A34A-0F871DED20D7}">
-      <text/>
-    </comment>
-    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{BD3F3EB6-950E-4F55-80F1-83C5155ED8C3}">
-      <text/>
-    </comment>
-    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{8D028038-0E98-4C33-A1FA-5D58A8AEA25A}">
-      <text/>
-    </comment>
-    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{E1047326-8403-419E-8F68-1A785BDB10CF}">
-      <text/>
-    </comment>
-    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{1053440D-8992-4492-A954-68065E307CBE}">
-      <text/>
-    </comment>
-    <comment ref="L14" authorId="0" shapeId="0" xr:uid="{7D1F1AFD-9A85-499D-BA8E-BC567CCD7FE5}">
-      <text/>
-    </comment>
-    <comment ref="M14" authorId="0" shapeId="0" xr:uid="{96276302-9FF8-43C3-852F-108D13251494}">
-      <text/>
-    </comment>
-    <comment ref="N14" authorId="0" shapeId="0" xr:uid="{A8476374-B41D-47AC-81E8-42DD7BB13531}">
-      <text/>
-    </comment>
-    <comment ref="O14" authorId="0" shapeId="0" xr:uid="{2C8D9E12-CED9-4751-98C1-823712278630}">
-      <text/>
-    </comment>
-    <comment ref="P14" authorId="0" shapeId="0" xr:uid="{2A3E31D6-2CC8-4800-9EB1-215163FC30BB}">
-      <text/>
+    <comment ref="N11" authorId="0" shapeId="0" xr:uid="{1ED944E3-70E5-418F-A642-9203A5122E09}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Embestida con Cuernos: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Ataque que es precedido por un movimiento mínimo de 1 metro, aumenta el daño 1d4 por cada metro  recorrido en línea recta hasta tu objetivo y hace daño perforante golpeando con los cuernos. El objetivo realiza una TS de su CON vs tu FZA, si falla es derribado . 2 RES.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{5661295B-121D-4C72-9D46-E2DE6DB9F09D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">El Llamado de los Cadáveres: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Puedes levantar no-muertos a partir de cadáveres que se encuentren hasta 20 metros a tu alrededor, alza un máximo de 1d4+1d4 por cada 2 niveles. 3 de maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C14" authorId="0" shapeId="0" xr:uid="{29EE3406-84E4-4FA9-BDB8-EE2E3B318A1D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Zona de no-muerte: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(Conjuro) Hace que una zona de 10 metros de radio imite las leyes del plano de la no muerte. Todos los no-muertos, infernales o ignotos dentro de ella recuperan 1d8 puntos de vida +1d4 por cada 4 niveles. Todas las criaturas cuyos puntos de vida lleguen a cero y mueran que no sean no-muertos se levantan automáticamente como uno. Dura 3d4 turnos. 8 de maná. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{1EED3939-89F4-4299-8FEF-1BC0678FF667}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Destemporalización Temporal: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Encantamiento) Selecciona un objetivo a la vista, este hace una tirada de RESI vs tu valor de INT, si falla desaparece de la línea temporal durante 1d4 turnos +1 por cada 5 niveles. Durante lo que dure este efecto el objetivo es expulsado del tiempo y no tiene recuerdo alguno de lo ocurrido. 6 de Maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{FF2B2A4A-2BDA-4A46-BE9F-18CDCC15A5FC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Hurtar Hechizo: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Encantamiento) Realiza una tirada de INT vs la INT de un objetivo al alcance de la vista, si es exitosa tienes acceso para saber todas las habilidades de clase de éste, puedes elegir una de entre ella que sea de carácter mágico (que involucre maná) y robarla durante 1d6 turnos +1d6 por cada 4 niveles. Puedes utilizarla como si fuera tuya. 4 de maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{2961B428-CD8B-41D0-B3EB-F3E5ABED3638}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Forma Humanoide: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Conjuro) La criatura fuerza las líneas arcanas de manera violenta para que, a los sentidos del resto de criaturas, se vea como un ser humanoide en español de la raza, sexo y forma de su elección. Ciertas habilidades ligadas a la visión de su forma ignota no funcionan mientras tenga esta habilidad activa. Si un ser sospecha de el puede realizar una tirada de PER vs la INT de la criatura para intuir que la forma es falsa. Dura hasta que la criatura lo desactive o algo fuerce su desactivación. 5 de maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{7E22656B-689E-4005-ABAD-EBBD6217DFC5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Campo Psíquico: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Conjuro) Esta habilidad no requiere tirada de chance. Aumenta las defensas naturales de la criatura 16, 21, 9, 14, 20, 7. Se desactiva cuando la criatura lo desea o si es forzado por efectos como aturdir, dormir, miedo, etc. No tiene costo de maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{8EA6C68A-6B64-4947-B9DF-AF3CD5B3FE4E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Destierro: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Conjuro) Lanza proyectiles de energia de luz negra que al impactar en una criatura objetivo provocando que en dos turnos desaparezca de la existencia durante 1d6 turnos +1d4 turnos por cada 5 niveles, en su siguiente turno empieza a perder entidad, apareciendo borroso y extraño ante los sentidos de otras criaturas y en su siguiente turno se desmaterializa por el plazo que salió en los dados. Desaparece de la realidad durante este tiempo así que nadie recuerda o tiene consciencia de que exista. Si el taumaturgo muere o se aleja más de 30 mts del objetivo antes de que desaparezca el efecto se cancela. 5 de maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{90FDFBE4-0323-48C3-8FE0-51B61ADCE398}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Detectar Presencias: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Encantamiento) La criatura emite una onda mental que alcanza unos 250 mts aprox y puede conocer la ubicación de cada entidad animada que no sea constructo y algunos pocos detalles sobre sus pensamientos y su futuro. También conoce si hay alguna unidad invisible o en sigilo. 10 maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{5F3A9382-6D62-46F2-AF0B-135A59780278}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Telepatía (Ignotos): </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Puedes comunicarte con una criatura o un grupo de criaturas que puedas ver mediante tu mente y te escucharán como si les hablaran y de la misma manera pueden responderte sin necesidad de que conozcan el mismo idioma. Como añadido también puedes crear un vínculo permanente con una criatura (+1 por cada 3 niveles) que te lo permita y puedes comunicarte con ella mediante sus pensamientos sin importar las distancias.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{4D04E8CF-8B43-4E49-8D40-2C9E3E6B889B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Polimorfismo Profano: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Encantamiento) Intenta hechizar a una criatura que pueda ver, esta debe realizar una tirada de RESI vs la INT del taumaturgo, si el objetivo falla se transforma en un amasijo de carne desarmada con características de ignoto, agrega ignoto a sus tipos, pierde la capacidad de hablar y lanzar hechizos, si AGI baja a 1 y tiene desventaja en todas las tiradas para atacar y defender. Dura 3 turnos. 10 Maná.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L14" authorId="0" shapeId="0" xr:uid="{AE3F402D-1E73-4861-B10D-8AF66FFC4585}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Marca Maldita de la No-Muerte: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Requiere Crescente de Sangre) Toda craitura que no sea constructo, ignoto, elemental, arcano o no-muerto que sea cortado por la Crescente de Sangre queda marcado. Sin importar cuanto tiempo pase cuando la criatura marcada, siempre y cuando mantenga la maldición, al morir se levantará como un no-muerto bajo el control del portador de la guadaña, a no ser que este desee que conserve su voluntad.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M14" authorId="0" shapeId="0" xr:uid="{2E2E44C4-383E-4DE6-A8E4-62A39511E4A2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Visión del Final: (</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Encantamiento) Lanza este encantamiento sobre una criatura que no sea ignoto, no-muerto, elemental, constructo o arcano, esta realiza una tirada de RESI vs tu INT, si falla proyectas en su mente una escena donde se ve muriendo de una manera horrible, sufre de miedo durante 4 turnos de cualquier unidad, por lo que intentará huir de ellas, y pierde 1d6 puntos de cordura +1d6 por cada 5 niveles.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N14" authorId="0" shapeId="0" xr:uid="{41D06D88-D07C-44CF-BF98-D878211DC06B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Toque del Penitente: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">(Encantamiento) Este encantamiento requiere que toques a una criatura objetivo que no sea ignoto, no-muerto, elemental, constructo o arcano, esta realiza una tirada de RESI vs tu INT, si falla debe ocupar su próximo turno en atacarse a sí mismo con el arma que tenga a mano en un ataque común con su respectiva tirada. Al llegar el turno la criatura puede hacer una TS de INT con CD 26 para resistir el efecto y recuperar el control de su turno. El toque puede ser bloqueado. 3 de maná.  </t>
+        </r>
+      </text>
     </comment>
   </commentList>
 </comments>
@@ -5837,6 +5981,1388 @@
     <author>Lenovo</author>
   </authors>
   <commentList>
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{6C70779B-740F-4BE3-84BD-558B467D6848}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Impulso: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Se apoya fuertemente en sus piernas para aumentar 2 metros sus salto o desplazamiento +1 metro por cada 4 niveles. Se usa como acción de movimiento. 3 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{0479CB64-90BC-4D52-BD47-1EAB1EB2A981}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Vuela: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Pasivo)La criatura puede remontar vuelo utilizando alas o apéndices similares moviéndose tanta distancia como le permita su estadística de movimiento.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{D5A4CFAD-A461-4D93-AD6A-06AB44708DBC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Montable: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Pasivo) Esta criatura puede ser montada y dirigida por otra que cuente con el conocimiento de equitación.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{3E72F925-3B9A-4541-A24C-344C0436D937}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Agilidad Acuática: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Pasivo) Cuando la criatura se encuentra en el agua o bajo ella tiene un  bonus de agilidad igual a su nivel más su valor de fuerza.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{4254A6F7-B683-4049-B376-932F68CE2E47}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Viajero Incansable: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Pasivo) Bonus +8 de RES +4 por cada 4 niveles.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{26B59A2D-8524-428B-9F01-74B0FFC94BF9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Reflejos de Alimaña:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> (Pasivo) Tus tiradas de eludir tienen +8 y si son efectivas puedes utilizar 2 de RES para desplazarte un metro al eludir.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{AA49DE8C-E887-4CBC-B4F8-ED3111B6A86A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Trepamuros: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Pasivo) La criatura puede utilizar los pequeños vellos de sus patas, extremidades o extensiones similares para aderirse a superficies como paredes y techos y moverse libremente por ellas como si andara normalmente en el suelo.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{C694EB33-B2E9-45CB-8EC2-C6F2A7D14AE2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Surcar las Aguas: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Habilidad que se utiliza como acción de movimiento. Cuando la criatura está en un medio acuático puede acelerar y duplicar su velocidad máxima de movimiento durante ese turno. 2 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{5507532E-DCFC-4973-AEDF-6F97EAAB9D34}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Unidad de Enjambre: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Pasivo) La unidad está compuesta por múltiples criaturas que se mueven y actúan juntas como una nube de enjambre, el hecho de que no sea una sola provee ciertas defensas físicas al grupo, aumentando sus resistencias naturales 9, 4, 13, 0, 0, 8. También puede ocupar y atravesar espacios ocupados por otra unidad y huecos pequeños en lugares como muros y puertas.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{58B440A6-5BF5-41FE-936D-05752BA8992C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Hostigamiento de Enjambre: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Acción de movimiento donde el enjambre de criaturas ocupa el mismo espacio de movimiento que el objetivo, lo rodean en nube y se mueven con este si se mueve en cada turno. El objetivo tiene desventaja en sus ataques físicos y defensas. El atacante no necesita tiradas de chance de ataque cuerpo a cuerpo mientras esté en la posición de su objetivo pero solo puede atacarle a él. Ésta habilidad no necesita chance de tirada.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{4408EB69-0042-4B02-BCDF-B2084AD1961D}">
+      <text/>
+    </comment>
+    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{B942F10B-C607-492B-AB0B-86BBD185F98C}">
+      <text/>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{7ED212F6-84E3-4C2C-918B-28D2D102FAE9}">
+      <text/>
+    </comment>
+    <comment ref="O2" authorId="0" shapeId="0" xr:uid="{9BC69E51-9F30-46FC-9AB9-8DB69506E0C8}">
+      <text/>
+    </comment>
+    <comment ref="P2" authorId="0" shapeId="0" xr:uid="{E846C7CD-5982-4632-9EE8-FCDC4E694DD9}">
+      <text/>
+    </comment>
+    <comment ref="Q2" authorId="0" shapeId="0" xr:uid="{FC0ECFDE-C329-48E9-B30F-1C79EA22D9AB}">
+      <text/>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{053DD034-35EC-4808-B88E-CDCA5FC3109E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Vigilancia Rapaz: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Enfoca su visión en un objetivo como acción principal, durante 3 turnos no necesita chance de ataque contra esa criatura y obtiene crítico a partir de una tirada de 15. Si obtiene un resultado crítico añade 1d4 al daño +1d4 por cada 4 niveles.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{8B4CDBE7-AFB4-409F-96C1-616266BD0A5B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sentidos Felinos: (</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Pasivo) Tu visión en la oscuridad es casi perfecta, tus sentidos están tan desarrollados que no tienes desventaja para defenderte ataques por la espalda o de objetivos que estén oculto.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{9B0FC5DB-AB9E-41BF-97F3-77CFF33351D5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Oido Sensible: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Pasivo) Tu sentido de la audición está muy desarrollado, tienes +8 en las tiradas de SUP que involucren el oído y puedes percibir sonidos de hasta aprox 30 metros a tu alrededor si no hay nada que los ocluse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{54319BD4-2239-43AD-9A71-F1E8B19C5A18}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Olfato Sensible: (Pasivo) </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>La criatura tiene un desarrollado sentido del olfato. Puede rastrear criaturas, alimentos u otras cosas por su aroma si lo conoce de antemano, y percibir los olores en un radio de 25 mts aproximadamente para saber que hay en el entorno excepto que algo interfiera con los olores. Tienes un bonus +8 a las tiradas de supervivencia cuando son para rastrear a una criatura y utilizas el olfato.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{EC0782DB-18DA-4FEF-9634-8F63283A8075}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Piel Dura 1: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">(Pasivo) La piel de la criatura provee resistencias naturales de 4, 6, 2, 4, 4, 2.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{B12C2BA3-8285-4BC4-9CB7-11EF99819FCA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Plumaje Férreo: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">(Pasivo) El denso plumaje de la criatura otorga resistencias naturales de 8, 6, 5, 2, 8, 8.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{1542328A-CD48-4BAE-943C-5EAA6EC30DEE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Pelaje Recio: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Pasivo) El animal posee una gruesa piel y un pelaje con una densidad considerable que le proteje de los elemento aumentando sus defensas naturales 3, 3, 1, 8, 19, 12.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{39066C73-4046-4D77-B070-159F4C11522A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Piel Dura 2: (Pasivo) </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>La piel escamosa y resistente de la criatura le provee defensas, sobre todo a los daños físicos, que mejoran sus resistencias naturales 8, 5, 6, 3, 1, 2.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J5" authorId="0" shapeId="0" xr:uid="{2933E82F-9CB1-4497-82E0-0813C0834396}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Metabolismo Subacuático: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Pasivo) La criatura puede permanecer debajo del agua conteniento la respiración por un máximo de hasta 24 hs.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K5" authorId="0" shapeId="0" xr:uid="{9DE2F7F9-FC61-4818-876C-E5096C466AF8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Camuflaje: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(pasivo) La criatura tiene una bonificación de +5 a la estadística de  SIG +1 por cada 4 niveles.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L5" authorId="0" shapeId="0" xr:uid="{BD7AD65F-097A-40CB-AB9F-3210FC06FBF2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Visión Térmica (Bestias): </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Bestias) La criatura ve las marcas térmicas de las cosas, por lo que puede notar las cosas que emiten calor sin ningún problema. Puede también detectar a criaturas ocultas que emitan calor corporal.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M5" authorId="0" shapeId="0" xr:uid="{15A917B6-FACE-4026-8EB8-9DAC95146E47}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Ecolocación (Bestias): </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Pasivo) La criatura puede "ver" con sonido, emitiendo sonidos prácticamente inaudibles (si desea) de alta frecuencia que rebotan en objetos y crean imágenes acústicas en el cerebro, pudiendo prescindir de la vista cuando sea necesario, tiene un bonus +2 a percepción +2 cada 5 niveles.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N5" authorId="0" shapeId="0" xr:uid="{51A797BE-150E-456A-8713-E2C5F26FDF52}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Reflejos Ofídios: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Pasivo) La criatura posee gran gracilidad y precisión de movimientos. Tiene bonus +4 a al ataque cuerpo a cuerpo, +6 a eludir y +3 DES, +1 a cada bonus cada 5 niveles.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O5" authorId="0" shapeId="0" xr:uid="{D72548C4-A0AB-4F66-B586-55F397F9F247}">
+      <text/>
+    </comment>
+    <comment ref="P5" authorId="0" shapeId="0" xr:uid="{0B3F086E-8802-4233-8874-9683B5359CB2}">
+      <text/>
+    </comment>
+    <comment ref="Q5" authorId="0" shapeId="0" xr:uid="{480D4F80-9ACD-48FB-9FFD-4515B3DA036A}">
+      <text/>
+    </comment>
+    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{9ACC628E-CDD3-4C5A-8DD4-C80F6C69F6C5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Embestida con Astas: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Ataque que es precedido por un movimiento mínimo de 1 metro, aumenta el daño 1d6 por cada metro  recorrido en línea recta hasta tu objetivo y hace daño contundetnte golpeando con las astas de la cabeza. El objetivo realiza una TS de su CON vs tu FZA, si falla es derribado . 2 RES.2 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{8FBBA04B-C343-497C-ACAC-B32084792D00}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Mordida Feroz: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Realiza una tirada de ataque de daño perforante mordiendo a un objetivo, si impacta exitosamente el objetivo hace una tirada de CON vs tu DES, si falla aplica un sangrado igual a 1d6 + 1d4 extra por cada 4 niveles durante 3 turnos. 1 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{52F9D227-6B41-4974-A8D4-1AF220D7FAD3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Mordida Destajadora: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Ataca a un objetivo cuerpo a cuerpo con una mordida, si es exitosa hace daño perforante, y si supera una tirada de destreza con CD 12 provoca un sangrado de 1d8 por tres turnos + 1 turno por cada 4 niveles de la criatura.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{60D91A50-E4E1-47CF-B2B4-5D85A3B23ACF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Ataque a los Ojos: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Si el ataque impacta exitosamente, el objetivo queda cegado hasta el final de su siguiente turno, si es crítico dura dos turnos, 2 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{EAD670DA-339A-4966-A180-79D9EC123BF2}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Arañazo: Realiza un ataque cuerpo a cuerpo utilizando las garras, hace daño cortante +1d4. Si impacta exitosamente el objetivo hace una tirada de CON vs tu DES, si falla le produces un sangrado que hace 1d4 + 1d4 por cada 4 niveles durante 2 turnos. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{9210F280-B3F6-469B-9154-1FEBA73CC2BB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Ataque en Picada: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Solo funciona si la criatura está volando y si se ejecuta luego de una acción de movimiento. Da un bonus +3 para la chance de ataque cuerpo a cuerpo y aumenta el daño 1d4 + 1d4 por cada 2 metros recorridos hasta el objetivo.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{FD8C5B84-666F-4BE3-A396-50E4E19FAFAA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Mordida Apresante: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Ataque cuerpo a cuerpo en el que la criatura intenta atrapar fuertemente a un objetivo de una extremidad, hace daño contundente +1d10 en daño contundente, el objetivo hace una tirada de CON vs la FZA de la criatura atacante, si falla queda atrapada entre las fauces de este y queda con el estado de lisado afectanto la articulación apresada. En cada uno de los turnos del objetivo este puede intentar liberarse haciendo una tirada de FZA vs la Fza del atacante, en cada turno de el atacante este puede elegir realizar el daño de la habilidad nuevamente como acción principal. 3 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{4EFAC017-6E12-4EC4-8C75-C16539BB0A2A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Embestir (Bestias):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> Ataque que es precedido por un movimiento mínimo de 1 metro, aumenta el daño 1d4 por cada metro  recorrido en línea recta hasta tu objetivo y hace daño contundetnte, el objetivo realiza una TS de su CON vs tu FZA, si falla es derribado . 2 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J8" authorId="0" shapeId="0" xr:uid="{68ECB2AF-0C08-478A-BD7F-19C1110943E0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Patada Potente: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Lanza un poderoso ataque con las patas traseras y aumenta el daño 1d8 + 1d4 pr cada 4 niveles. Si el ataque es exitoso el objetivo debe hacer tres TS de su CON vs tu FZA, si falla la primera cae derribado, si falla la segunda es desplazado 2 mts hacia atras, si falla la tercera queda aturdido por 2 turnos. 4 RES.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K8" authorId="0" shapeId="0" xr:uid="{5CF43AD9-9604-435B-A6D9-DF69ACACB038}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Atrapar: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Realiza una tirada de ataque cuerpo a cuerpo contra un objetivo que esté al alcance de tus extremidades o cuerpo, si es exitosa no hace daño y el objetivo queda apresado en tu poder, con las extremidades superiores y inferiores inutilizadas, para safarse debe hacer una TS de FZA vs tu FZA como acción principal en su turno. 3 RES</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{432CEA68-1487-4940-A459-E1D8745EA479}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Constricción: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Cuando tienes una criatura atrapada con tu cuerpo o extremidades puedes utilizar tu acción de movimiento para apretarla fuertemente, esta acción no tiene TS y hace tu daño cuerpo a cuerpo en contundente, daña también la resistencia del objetivo. 3 RES</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{D95B8ACC-920B-4A64-968D-E41813BB9C61}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Giro Mortal: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>No necesita chance de ataque. Es necesario que la criatura tenga al objetivo atrapado entre sus fauces. Gira sobre si mismo y hace daño contundente directamente, si realiza este ataque efectivamente durante dos o más turnos consecutivos a partir del segundo realiza una tirada de FZA vs CON del objetivo, si es exitoso dos veces seguida le arranca la extremidad en la que lo tiene atrapado y le produce un sangrado de 1d12 durante 10 turnos, 3 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N8" authorId="0" shapeId="0" xr:uid="{01621E41-16A3-41FE-B520-347D09035EAC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Embestida con Cuernos: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Ataque que es precedido por un movimiento mínimo de 1 metro, aumenta el daño 1d4 por cada metro  recorrido en línea recta hasta tu objetivo y hace daño perforante golpeando con los cuernos. El objetivo realiza una TS de su CON vs tu FZA, si falla es derribado . 2 RES.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O8" authorId="0" shapeId="0" xr:uid="{B57CCE3A-CBD2-450F-8B68-3A5D4CFD4FF2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Pisotón (Bestias): </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Habilidad de ataque cuerpo a cuerpo en la que la criatura intenta aplastar con su pata a una criatura cuya clasificación de tamaño sea inferior. Hace daño contundente de base +1d8 +1d6 por cada 5 puntos de FZA por sobre la CON del objetivo +1d6 por cada nivel de tamaño por encima del objetivo y derriba a este, quien luego hace una tirada de RESI vs FZA del atacante, si falla queda aturdido por 2 turnos. Solo puede ser bloqueado por escudo. Si el atacante lo desea, y el ataque es efectivo, puede moverse al cuadro del objetivo y mantener su pata sobre este para mantenerlo atrapado, en cada turno del atacante hace daño base contundente, en cada turno del objetivo este puede hacer una tirada de FZA vs CON del atacante para liberarse.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P8" authorId="0" shapeId="0" xr:uid="{F29A1B3D-7871-4EDE-88C3-533FC787DB76}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Mordida Carroñera: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>La criatura vive a base del consumo de carne como dieta principal. Puede utilizarlas en una mordida en ataque cuerpo a cuerpo, con su respectiva tirada de chance, hace daño base cortante +1d4, +1d4 por cada 4 niveles, y se cura VID y RES la mitad de los puntos de daño que haga siendo el mínimo 1 y redondeando hacia abajo.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q8" authorId="0" shapeId="0" xr:uid="{B5285EE7-F3FF-44E2-80CD-0B56040F4457}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Picadura Hematófaga: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Ataque cuerpo a cuerpo en el cual el atacante hace daño perforante y absorbe una cierta cantidad de sangre. Quita tantos puntos de RES como VIDA haya quitado y aumenta estos a la VIDA del atacante. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R8" authorId="0" shapeId="0" xr:uid="{D091F5DA-68A2-416D-9A4C-221946240E94}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Corte Lacerante: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Abre una herida con un apéndice cortante haciendo la respectiva tirada de chance, si es efectivo hace daño base cortante e inflinje un sangrado de 1d4 + 1d4 por cada 4 puntos de destreza posea.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{B1C35BED-8494-476B-BB74-593308B26769}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Grunido: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Haces una tirada de INT vs RESI del objetivo, si este falla queda asustado por1 turno +1 por cada 4 puntos de FZA.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{F909FA28-53B1-463B-BBDF-3B836856BC8A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Graznido de Alerta: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Alerta a todos los enemigos cercanos en un radio de 30 metros, todos los aliados no tienen desventajas al ser atacados por la espalda o por unidades ocultas.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{C11A6A66-B051-4F54-A174-016C1E41BCB3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Guardián: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Puede rastrear criaturas por su olor si lo conoce de antemano. Tienes un bonus +8 a las tiradas de supervivencia cuando son para rastrear a una criatura y utilizas el olfato o el oído.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{1931BF49-AD06-4957-927F-7A1E278AB06B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Mensajero Animal: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Pasivo) Puede seguir y recordar rutas.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{84C2EABE-A96E-4BB1-A961-79BFF44216C8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Imitación:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> (Pasivo) La criatura puede imitar voces humanas, un humanoide con ciertos conocimiento puede enseñarle a para que repita lo dicho, el animal comprenderá solo parcialmente algunas palabras como "comida" o cosas por el estilo, pero no frases completas.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{6848059F-15DE-49F4-A6D4-C49FD31B9BF7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Bestia de Carga: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">(Pasivo) Esta criatura puede llevar mochilas y bolsas con objetos con un inventario propio y acumular una cantidad de peso igual a 5 veces su valor de fuerza. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{B4FE115A-8F06-4ACE-8ABA-1DC7110D7C40}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Molestar y Perturbar: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">(Pasivo) Cuando la criatura está ocupando el mismo lugar que otra esta última tiene desventaja al realizar acciones que tengan como objetivo a otra criatura que no sea la que porta la habilidad, tampoco puede entrar en concentración. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{DB87FC78-B3DA-4E70-879A-7C1C3AB94A68}">
+      <text/>
+    </comment>
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{9AA409D8-1F48-43CD-9362-45E8FB3F7E30}">
+      <text/>
+    </comment>
+    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{11D589E4-07A2-45B9-925C-E806FF23824D}">
+      <text/>
+    </comment>
+    <comment ref="L11" authorId="0" shapeId="0" xr:uid="{CFE920E3-F0EE-4CD3-A16F-17D6BB45398C}">
+      <text/>
+    </comment>
+    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{6E925165-6DDC-4A82-8DB3-C750D342974E}">
+      <text/>
+    </comment>
+    <comment ref="N11" authorId="0" shapeId="0" xr:uid="{81B5587D-C3EA-437A-A3FB-AC0214E9408D}">
+      <text/>
+    </comment>
+    <comment ref="O11" authorId="0" shapeId="0" xr:uid="{3D7FB5C6-2D8F-4AAF-8BDB-606AF97A2751}">
+      <text/>
+    </comment>
+    <comment ref="P11" authorId="0" shapeId="0" xr:uid="{8C8897CD-C875-4DBC-8F25-EC1031BA6A3B}">
+      <text/>
+    </comment>
+    <comment ref="Q11" authorId="0" shapeId="0" xr:uid="{F03211AE-9F6F-45A6-8394-E81E7FA13869}">
+      <text/>
+    </comment>
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{EF850E00-659B-4047-A8D9-DBD9C6355512}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Transmisor de Peste Infecciosa: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>(Pasivo) Cada vez que un ataque cuerpo a cuerpo con dientes o garras dañe a un oponte este realiza una tirada de CON con DC 7, si falla tiene la enfermedad Peste Infecciosa, cada turno repite la tirada de CON, si falla pierde 1d4 puntos de vida.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C14" authorId="0" shapeId="0" xr:uid="{90F07E64-EDC6-4D03-B256-1D44FE5CBEAE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Veneno 1: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Lanza un ataque común cuerpo a cuerpo realizado con el órgano en el cual porta veneno haciendo el daño correspondente, luego realiza una tirada de DES vs la CON del objetivo, si es exitosa envenena y hace 1d4 de daño durante5 turnos +1 turno por cada 4 niveles. 1 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{80985EDB-18D6-4997-A511-ACCA4964F04C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Ácido Corrosivo: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>La criatura vomita un jugo estómacal extremadamente corrosivo, debe efectuar una tirada de chance de ataque a distancia. Puede bloquearse con escudo pero si impacta en este o si cae sobre una parte de la armadura (a criterio azaroso decisión del DM) el portador hace una tirada de DES con CD 14, si falla la pieza alcanzada puede dañarse y quedar inutilizada. Hace 1d8 de daño de fuego +1d6 por cada 4 niveles. 2 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{257C9967-340B-4F16-8DD7-250D0EA9F134}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Ponzoña: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>La criatura pica con su aguijón o apéndice en punta con veneno haciendo la respectiva tirada cuerpo a cuerpo con un bonus +5 a la tirada de chance +1 por cada 3 niveles. Si el ataque es efectivo hace daño base en perforante y aplica una poderosa toxina que hace 1d4 -1  de daño, +1d4 por cada 4 niveles, durante 6 turnos, +1 por cada 4 niveles, provoca dolor por lo cual el objetivo no puede entrar en concentración y tiene -5 a las tiradas de chance de conjuros y encantamientos, +1 por cada 4 niveles. 1 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{256EBAD5-3AA3-448B-96A3-16D016F0B14F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Veneno 1: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Lanza un ataque común cuerpo a cuerpo realizado con el órgano en el cual porta veneno haciendo el daño correspondente, luego realiza una tirada de DES vs la CON del objetivo, si es exitosa envenena y hace 1d8 de daño durante 5 turnos +1 turno por cada 4 niveles. 1 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{800013D1-AE8B-48C5-A34A-0F871DED20D7}">
+      <text/>
+    </comment>
+    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{BD3F3EB6-950E-4F55-80F1-83C5155ED8C3}">
+      <text/>
+    </comment>
+    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{8D028038-0E98-4C33-A1FA-5D58A8AEA25A}">
+      <text/>
+    </comment>
+    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{E1047326-8403-419E-8F68-1A785BDB10CF}">
+      <text/>
+    </comment>
+    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{1053440D-8992-4492-A954-68065E307CBE}">
+      <text/>
+    </comment>
+    <comment ref="L14" authorId="0" shapeId="0" xr:uid="{7D1F1AFD-9A85-499D-BA8E-BC567CCD7FE5}">
+      <text/>
+    </comment>
+    <comment ref="M14" authorId="0" shapeId="0" xr:uid="{96276302-9FF8-43C3-852F-108D13251494}">
+      <text/>
+    </comment>
+    <comment ref="N14" authorId="0" shapeId="0" xr:uid="{A8476374-B41D-47AC-81E8-42DD7BB13531}">
+      <text/>
+    </comment>
+    <comment ref="O14" authorId="0" shapeId="0" xr:uid="{2C8D9E12-CED9-4751-98C1-823712278630}">
+      <text/>
+    </comment>
+    <comment ref="P14" authorId="0" shapeId="0" xr:uid="{2A3E31D6-2CC8-4800-9EB1-215163FC30BB}">
+      <text/>
+    </comment>
+    <comment ref="Q14" authorId="0" shapeId="0" xr:uid="{F643EF57-AFB2-4CB6-8ECD-426DAC92EE99}">
+      <text/>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Lenovo</author>
+  </authors>
+  <commentList>
     <comment ref="B2" authorId="0" shapeId="0" xr:uid="{EF61C965-83B5-42CB-8874-E80F6B1F2EEF}">
       <text>
         <r>
@@ -7316,7 +8842,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="121">
   <si>
     <t>MOVIMIENTO</t>
   </si>
@@ -7618,9 +9144,6 @@
     <t>Mordida Carroñera</t>
   </si>
   <si>
-    <t>Picadura Hematófaga</t>
-  </si>
-  <si>
     <t>Veneno 2</t>
   </si>
   <si>
@@ -7676,6 +9199,12 @@
   </si>
   <si>
     <t>Automatísmo Arcano</t>
+  </si>
+  <si>
+    <t>Mordedura  Hematófaga</t>
+  </si>
+  <si>
+    <t>Corte Lacerante</t>
   </si>
 </sst>
 </file>
@@ -7958,15 +9487,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7980,6 +9500,15 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9164,14 +10693,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>38099</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>345700</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>5521</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>723900</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>331694</xdr:rowOff>
+      <xdr:rowOff>345301</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -9200,8 +10729,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1562099" y="345700"/>
-          <a:ext cx="685801" cy="680759"/>
+          <a:off x="1562099" y="359307"/>
+          <a:ext cx="685801" cy="693565"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10063,9 +11592,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>23811</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>342900</xdr:rowOff>
+      <xdr:colOff>23812</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>16330</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="709612" cy="699527"/>
     <xdr:pic>
@@ -10095,7 +11624,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="785811" y="4511488"/>
+          <a:off x="785812" y="4615544"/>
           <a:ext cx="709612" cy="699527"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -11042,6 +12571,106 @@
         <a:xfrm>
           <a:off x="5361214" y="3551464"/>
           <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>40822</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>16328</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>724822</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>346542</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="45" name="Imagen 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BBABC91-8F8F-50E9-77D9-A5954FAA24BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId50" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12232822" y="2492828"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>46224</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>730224</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>338019</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Imagen 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AECF5445-C373-4EAC-B134-359484A4D50B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId51" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13000224" y="2442882"/>
+          <a:ext cx="684000" cy="674196"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -13589,7 +15218,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D5F5BAF-BE93-4F06-A7C2-0B0CBE1C14C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DE8628E-6F72-4893-B5B5-BE8FC6C970D6}">
   <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13597,18 +15226,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>118</v>
-      </c>
+      <c r="A1" s="22"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
@@ -13621,7 +15242,7 @@
       <c r="N1" s="7"/>
     </row>
     <row r="2" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
+      <c r="A2" s="23"/>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
@@ -13637,7 +15258,7 @@
       <c r="N2" s="15"/>
     </row>
     <row r="3" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
+      <c r="A3" s="24"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -13653,7 +15274,7 @@
       <c r="N3" s="16"/>
     </row>
     <row r="4" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20"/>
+      <c r="A4" s="17"/>
       <c r="B4" s="14"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -13669,7 +15290,7 @@
       <c r="N4" s="7"/>
     </row>
     <row r="5" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
+      <c r="A5" s="18"/>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
@@ -13685,7 +15306,7 @@
       <c r="N5" s="15"/>
     </row>
     <row r="6" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
+      <c r="A6" s="19"/>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -13701,7 +15322,7 @@
       <c r="N6" s="16"/>
     </row>
     <row r="7" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -13717,12 +15338,12 @@
       <c r="N7" s="7"/>
     </row>
     <row r="8" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
-      <c r="F8" s="23"/>
+      <c r="F8" s="20"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
@@ -13733,12 +15354,12 @@
       <c r="N8" s="15"/>
     </row>
     <row r="9" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="24"/>
+      <c r="F9" s="21"/>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
@@ -13750,7 +15371,7 @@
       <c r="R9" s="10"/>
     </row>
     <row r="10" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="20"/>
+      <c r="A10" s="17"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -13766,7 +15387,7 @@
       <c r="N10" s="7"/>
     </row>
     <row r="11" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
+      <c r="A11" s="18"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
@@ -13782,7 +15403,7 @@
       <c r="N11" s="15"/>
     </row>
     <row r="12" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
+      <c r="A12" s="19"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
@@ -13798,7 +15419,7 @@
       <c r="N12" s="16"/>
     </row>
     <row r="13" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="9"/>
@@ -13814,7 +15435,7 @@
       <c r="N13" s="7"/>
     </row>
     <row r="14" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
+      <c r="A14" s="18"/>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -13830,7 +15451,7 @@
       <c r="N14" s="15"/>
     </row>
     <row r="15" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
+      <c r="A15" s="19"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
@@ -13919,12 +15540,347 @@
     <mergeCell ref="F2:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D5F5BAF-BE93-4F06-A7C2-0B0CBE1C14C1}">
+  <dimension ref="A1:R15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="11.42578125" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+    </row>
+    <row r="2" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="23"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+    </row>
+    <row r="3" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="24"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+    </row>
+    <row r="4" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+    </row>
+    <row r="5" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+    </row>
+    <row r="6" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="19"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+    </row>
+    <row r="7" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="17"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+    </row>
+    <row r="8" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+    </row>
+    <row r="9" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="19"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="R9" s="10"/>
+    </row>
+    <row r="10" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="17"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+    </row>
+    <row r="11" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+    </row>
+    <row r="12" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="19"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+    </row>
+    <row r="13" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="17"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+    </row>
+    <row r="14" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+    </row>
+    <row r="15" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="19"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="70">
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9F6337B-89AA-4305-B4A8-6D5D44FBF989}">
   <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -13933,9 +15889,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17"/>
+      <c r="A1" s="22"/>
       <c r="B1" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -13951,7 +15907,7 @@
       <c r="N1" s="7"/>
     </row>
     <row r="2" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
+      <c r="A2" s="23"/>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
@@ -13967,7 +15923,7 @@
       <c r="N2" s="15"/>
     </row>
     <row r="3" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
+      <c r="A3" s="24"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -13983,12 +15939,12 @@
       <c r="N3" s="16"/>
     </row>
     <row r="4" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20"/>
+      <c r="A4" s="17"/>
       <c r="B4" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
@@ -14003,7 +15959,7 @@
       <c r="N4" s="7"/>
     </row>
     <row r="5" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
+      <c r="A5" s="18"/>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
@@ -14019,7 +15975,7 @@
       <c r="N5" s="15"/>
     </row>
     <row r="6" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
+      <c r="A6" s="19"/>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -14035,20 +15991,20 @@
       <c r="N6" s="16"/>
     </row>
     <row r="7" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
-        <v>112</v>
+      <c r="A7" s="17" t="s">
+        <v>111</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>107</v>
-      </c>
       <c r="D7" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="7"/>
@@ -14061,12 +16017,12 @@
       <c r="N7" s="7"/>
     </row>
     <row r="8" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
-      <c r="F8" s="23"/>
+      <c r="F8" s="20"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
@@ -14077,12 +16033,12 @@
       <c r="N8" s="15"/>
     </row>
     <row r="9" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="24"/>
+      <c r="F9" s="21"/>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
@@ -14094,18 +16050,18 @@
       <c r="R9" s="10"/>
     </row>
     <row r="10" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="20"/>
+      <c r="A10" s="17"/>
       <c r="B10" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>114</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>115</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
@@ -14118,7 +16074,7 @@
       <c r="N10" s="7"/>
     </row>
     <row r="11" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
+      <c r="A11" s="18"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
@@ -14134,7 +16090,7 @@
       <c r="N11" s="15"/>
     </row>
     <row r="12" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
+      <c r="A12" s="19"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
@@ -14150,7 +16106,7 @@
       <c r="N12" s="16"/>
     </row>
     <row r="13" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="9"/>
@@ -14166,7 +16122,7 @@
       <c r="N13" s="7"/>
     </row>
     <row r="14" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
+      <c r="A14" s="18"/>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -14182,7 +16138,335 @@
       <c r="N14" s="15"/>
     </row>
     <row r="15" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="70">
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{258ECD2D-C047-4967-AAA4-94D91ED5B3F1}">
+  <dimension ref="A1:R15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="11.42578125" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+    </row>
+    <row r="2" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="23"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+    </row>
+    <row r="3" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="24"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+    </row>
+    <row r="4" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+    </row>
+    <row r="5" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+    </row>
+    <row r="6" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="19"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+    </row>
+    <row r="7" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="17"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+    </row>
+    <row r="8" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+    </row>
+    <row r="9" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="19"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="R9" s="10"/>
+    </row>
+    <row r="10" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="17"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+    </row>
+    <row r="11" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+    </row>
+    <row r="12" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="19"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+    </row>
+    <row r="13" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="17"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+    </row>
+    <row r="14" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+    </row>
+    <row r="15" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="19"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
@@ -14271,348 +16555,20 @@
     <mergeCell ref="F2:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{258ECD2D-C047-4967-AAA4-94D91ED5B3F1}">
-  <dimension ref="A1:R15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="16384" width="11.42578125" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17"/>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-    </row>
-    <row r="2" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-    </row>
-    <row r="3" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
-    </row>
-    <row r="4" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-    </row>
-    <row r="5" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-    </row>
-    <row r="6" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-    </row>
-    <row r="7" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-    </row>
-    <row r="8" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-    </row>
-    <row r="9" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="R9" s="10"/>
-    </row>
-    <row r="10" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="20"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-    </row>
-    <row r="11" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-    </row>
-    <row r="12" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-    </row>
-    <row r="13" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-    </row>
-    <row r="14" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-    </row>
-    <row r="15" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-    </row>
-  </sheetData>
-  <mergeCells count="70">
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4001897D-342F-41B7-B37C-50A8A68A41B2}">
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:R74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="27.95" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
@@ -14648,9 +16604,10 @@
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
     </row>
-    <row r="2" spans="1:17" ht="27.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="18"/>
+    <row r="2" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="23"/>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
@@ -14666,9 +16623,10 @@
       <c r="N2" s="15"/>
       <c r="O2" s="15"/>
       <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
     </row>
-    <row r="3" spans="1:17" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="19"/>
+    <row r="3" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="24"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -14684,10 +16642,10 @@
       <c r="N3" s="16"/>
       <c r="O3" s="16"/>
       <c r="P3" s="16"/>
-      <c r="Q3" s="2"/>
+      <c r="Q3" s="16"/>
     </row>
-    <row r="4" spans="1:17" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="20" t="s">
+    <row r="4" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
@@ -14731,10 +16689,10 @@
       </c>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
-      <c r="Q4" s="3"/>
+      <c r="Q4" s="7"/>
     </row>
-    <row r="5" spans="1:17" ht="27.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="21"/>
+    <row r="5" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="18"/>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
@@ -14750,10 +16708,10 @@
       <c r="N5" s="15"/>
       <c r="O5" s="15"/>
       <c r="P5" s="15"/>
-      <c r="Q5" s="3"/>
+      <c r="Q5" s="15"/>
     </row>
-    <row r="6" spans="1:17" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="22"/>
+    <row r="6" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="19"/>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -14769,10 +16727,10 @@
       <c r="N6" s="16"/>
       <c r="O6" s="16"/>
       <c r="P6" s="16"/>
-      <c r="Q6" s="3"/>
+      <c r="Q6" s="16"/>
     </row>
-    <row r="7" spans="1:17" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="20" t="s">
+    <row r="7" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A7" s="17" t="s">
         <v>1</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -14788,7 +16746,7 @@
         <v>77</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>76</v>
@@ -14821,16 +16779,19 @@
         <v>99</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>100</v>
+        <v>119</v>
+      </c>
+      <c r="R7" s="7" t="s">
+        <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="27.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="21"/>
+    <row r="8" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="18"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
-      <c r="F8" s="23"/>
+      <c r="F8" s="20"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
@@ -14842,14 +16803,15 @@
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
       <c r="Q8" s="15"/>
+      <c r="R8" s="15"/>
     </row>
-    <row r="9" spans="1:17" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="22"/>
+    <row r="9" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A9" s="19"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="24"/>
+      <c r="F9" s="21"/>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
@@ -14861,9 +16823,10 @@
       <c r="O9" s="16"/>
       <c r="P9" s="16"/>
       <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
     </row>
-    <row r="10" spans="1:17" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="20" t="s">
+    <row r="10" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A10" s="17" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="7" t="s">
@@ -14885,7 +16848,7 @@
         <v>92</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
@@ -14895,10 +16858,10 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
-      <c r="Q10" s="3"/>
+      <c r="Q10" s="7"/>
     </row>
-    <row r="11" spans="1:17" ht="27.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="21"/>
+    <row r="11" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="18"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
@@ -14914,10 +16877,10 @@
       <c r="N11" s="15"/>
       <c r="O11" s="15"/>
       <c r="P11" s="15"/>
-      <c r="Q11" s="3"/>
+      <c r="Q11" s="15"/>
     </row>
-    <row r="12" spans="1:17" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="22"/>
+    <row r="12" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="19"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
@@ -14933,10 +16896,10 @@
       <c r="N12" s="16"/>
       <c r="O12" s="16"/>
       <c r="P12" s="16"/>
-      <c r="Q12" s="3"/>
+      <c r="Q12" s="16"/>
     </row>
-    <row r="13" spans="1:17" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="20" t="s">
+    <row r="13" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="17" t="s">
         <v>59</v>
       </c>
       <c r="B13" s="13" t="s">
@@ -14952,7 +16915,7 @@
         <v>98</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
@@ -14964,10 +16927,10 @@
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
-      <c r="Q13" s="3"/>
+      <c r="Q13" s="7"/>
     </row>
-    <row r="14" spans="1:17" ht="27.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="21"/>
+    <row r="14" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="18"/>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -14983,10 +16946,10 @@
       <c r="N14" s="15"/>
       <c r="O14" s="15"/>
       <c r="P14" s="15"/>
-      <c r="Q14" s="3"/>
+      <c r="Q14" s="15"/>
     </row>
-    <row r="15" spans="1:17" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="22"/>
+    <row r="15" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A15" s="19"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
@@ -15002,9 +16965,9 @@
       <c r="N15" s="16"/>
       <c r="O15" s="16"/>
       <c r="P15" s="16"/>
-      <c r="Q15" s="4"/>
+      <c r="Q15" s="16"/>
     </row>
-    <row r="16" spans="1:17" ht="27.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -16008,37 +17971,47 @@
       <c r="Q74" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="81">
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B5:B6"/>
+  <mergeCells count="86">
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="P14:P15"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="I5:I6"/>
@@ -16055,41 +18028,36 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="H5:H6"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="P14:P15"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="M2:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -16097,7 +18065,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A120AE4-F77F-45D1-8625-8458A9342776}">
   <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -16106,7 +18074,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="22" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="7" t="s">
@@ -16146,7 +18114,7 @@
       <c r="N1" s="7"/>
     </row>
     <row r="2" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
+      <c r="A2" s="23"/>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
@@ -16162,7 +18130,7 @@
       <c r="N2" s="15"/>
     </row>
     <row r="3" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
+      <c r="A3" s="24"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -16178,7 +18146,7 @@
       <c r="N3" s="16"/>
     </row>
     <row r="4" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="17" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="7" t="s">
@@ -16220,7 +18188,7 @@
       <c r="N4" s="7"/>
     </row>
     <row r="5" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
+      <c r="A5" s="18"/>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
@@ -16236,7 +18204,7 @@
       <c r="N5" s="15"/>
     </row>
     <row r="6" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
+      <c r="A6" s="19"/>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -16252,7 +18220,7 @@
       <c r="N6" s="16"/>
     </row>
     <row r="7" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -16280,12 +18248,12 @@
       <c r="N7" s="7"/>
     </row>
     <row r="8" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
-      <c r="F8" s="23"/>
+      <c r="F8" s="20"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
@@ -16296,12 +18264,12 @@
       <c r="N8" s="15"/>
     </row>
     <row r="9" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="24"/>
+      <c r="F9" s="21"/>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
@@ -16313,7 +18281,7 @@
       <c r="R9" s="10"/>
     </row>
     <row r="10" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B10" s="7" t="s">
@@ -16339,7 +18307,7 @@
       <c r="N10" s="7"/>
     </row>
     <row r="11" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
+      <c r="A11" s="18"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
@@ -16355,7 +18323,7 @@
       <c r="N11" s="15"/>
     </row>
     <row r="12" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
+      <c r="A12" s="19"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
@@ -16371,7 +18339,7 @@
       <c r="N12" s="16"/>
     </row>
     <row r="13" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="17" t="s">
         <v>7</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -16415,7 +18383,7 @@
       </c>
     </row>
     <row r="14" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
+      <c r="A14" s="18"/>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -16431,7 +18399,7 @@
       <c r="N14" s="15"/>
     </row>
     <row r="15" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
+      <c r="A15" s="19"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
@@ -16448,6 +18416,64 @@
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -16460,64 +18486,6 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Excels compiladores de habilidades/Habilidades de criaturas no humanoides.xlsx
+++ b/Excels compiladores de habilidades/Habilidades de criaturas no humanoides.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\arkanor-assets\Excels compiladores de habilidades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0F8B5D-E7C1-4DC9-AF63-6514988ED004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4738EAE-1655-4FB5-9C1C-27690AED7CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4E5D0542-3908-4101-9CFE-772E035496F2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{4E5D0542-3908-4101-9CFE-772E035496F2}"/>
   </bookViews>
   <sheets>
     <sheet name="No-Muerto" sheetId="8" r:id="rId1"/>
@@ -3030,30 +3030,30 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">La criatura realiza un ataque cuerpo a cuerpo que no produce daño pero intenta introducir su materia nubosa dentro de una criatura que no sea constructo, ignoto, celestial o arcano y controlarlo. Para que sea efectivo además de que la chance cuerpo a cuerpo sea exitosa, debe hacer tiradas d20 de inteligencia como parte de la misma acción principal, debe superar los puntos de vida actuales y los puntos de resilencia del objetivo sumados, si acumula tres fallos fallará en la posesión, si acumula tres éxitos el infernal se introduce completamente dentro de su víctima, esta convulsiona brevemente durante unos segundos y el infernal toma total control del cuerpo de la criatura y se vuelven una sola unidad, las estadísticas de FZA, AGI y CON son las de la víctima y CAR, INT y SAB del infernal. El objetivo no esta muerto, pero su consciencia se encuentra dormida, el infernal adopta la clase de este, añadiendo el tipo ignoto a los tipos que ya tiene y la inscripción "poseído/a" despues del nombre. 3 RES. </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{55A8DA2F-4870-4E20-8F41-AB141DE2BB42}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Baba Cegadora: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Ataque a distancia, la criatura lanza un escupitajo a un punto que pueda ver a 15 metros máximo de él, si el objetivo es otra criatura lo dirige directamente a los ojos. Si el ataque es exitoso el objetivo debe superar una tirada de salvación de Destreza CD 13 para no quedar cegadas hasta el final del siguiente turno del lanzador. 2 Res.</t>
+          <t xml:space="preserve">La criatura realiza un ataque cuerpo a cuerpo que no produce daño pero intenta introducir su materia nubosa dentro de una criatura que no sea constructo, ignoto, celestial o arcano y controlarlo. Para que sea efectivo además de que la chance cuerpo a cuerpo sea exitosa, debe hacer tiradas d20 de inteligencia como parte de la misma acción principal, debe superar los puntos de vida actuales y los puntos de resilencia del objetivo sumados, si acumula tres fallos fallará en la posesión, si acumula tres éxitos el infernal se introduce completamente dentro de su víctima, esta convulsiona brevemente durante unos segundos y el infernal toma total control del cuerpo de la criatura y se vuelven una sola unidad, las estadísticas de FZA, AGI y CON son las de la víctima y CAR, INT y SAB del infernal. El objetivo no esta muerto, pero su consciencia se encuentra dormida, el infernal adopta la clase de este, añadiendo el tipo infernal a los tipos que ya tiene y la inscripción "poseído/a" despues del nombre. 3 RES. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{47FBAF54-F20C-4D8E-B27C-16905CA85768}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Inducción en Llamas: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">La criatura realiza un ataque cuerpo a cuerpo que no produce daño pero intenta introducir su materia ardiente dentro de una criatura que no sea constructo, celestial o arcano y encenderlo en llamas. Para que sea efectivo además de que la chance cuerpo a cuerpo sea exitosa, debe hacer varias tiradas d20 de AGI como parte de la misma acción principal, debe superar los puntos de vida actuales y los puntos de resilencia del objetivo sumados, si acumula tres fallos fallará en la inducción, si acumula tres éxitos el infernal se introduce completamente dentro de su víctima, esta convulsiona brevemente durante unos segundos y el infernal se introduce control del cuerpo de la criatura y se vuelven una sola unidad, en cada uno de los turnos de la criatura el infernal tira su chance cuerpo a cuerpo, si es efectiva hace su daño cuerpo a cuerpo en fuego y traspasa la armadura, pero no las defensas naturales. El infernal puede salir cuando quiera a un cuadro inmediatamente al lado de su objetivo ocupando su acción principal. El objetivo puede hacer tiradas de CON vs la FZA como acción principal en cada uno de sus turnos para obligar al infernal a que salga de su cuerpo en ese turno mismo. 3 RES. </t>
         </r>
       </text>
     </comment>
@@ -3745,26 +3745,27 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{4B13328E-2E30-434E-A45D-77DC5FC28107}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Embestida Brutal: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="18"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Ataque precedido por la acción de movimiento la cual debe recorrer mínimamente 1 metro. Hace daño base en contundente con un bonus de 1d6 +1d6 por cada 4 puntos de CON. Si el ataque impacta o es bloqueado por el objetivo este debe hacer una tirada de CON vs la FZA del atacante, si falla es desplazado 2 metros, +1 por cada 5 puntos de fuerza del atacante, y queda derribado y aturdido por 1 turno. 3 RES.</t>
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{50DA1648-5D7C-433C-8758-8020AF2D1368}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Ataque con Garras: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">La criatura puede atacar en un turno tantas veces como extremidades con garras tenga con un mínimo de 1. Cada ataque exitoso o bloqueado hace un daño extra de 1d4 +1d4 por cada 4 puntos de FZA tenga la criatura. Si fue exitoso arde 1d4 por tantos turnos como niveles tenga la criatura atacante. 2 RES.
+</t>
         </r>
       </text>
     </comment>
@@ -8842,7 +8843,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="123">
   <si>
     <t>MOVIMIENTO</t>
   </si>
@@ -9206,6 +9207,12 @@
   <si>
     <t>Corte Lacerante</t>
   </si>
+  <si>
+    <t>Garras Ardientes</t>
+  </si>
+  <si>
+    <t>Inducción Infernal</t>
+  </si>
 </sst>
 </file>
 
@@ -9687,15 +9694,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>44822</xdr:colOff>
+      <xdr:colOff>33616</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>11207</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>728822</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>336618</xdr:rowOff>
+      <xdr:colOff>717616</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>442</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -9724,7 +9731,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="806822" y="347383"/>
+          <a:off x="795616" y="358589"/>
           <a:ext cx="684000" cy="684000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -10125,6 +10132,106 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1568824" y="3485030"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>44824</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>728824</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>336617</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Imagen 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{828DB0F3-CA86-B5D2-9416-9387C9544E01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3854824" y="2431676"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>33618</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>717618</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>336617</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Imagen 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12489AB1-27EE-BB3C-F888-6EB2A8BB9D3F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1557618" y="347382"/>
           <a:ext cx="684000" cy="684000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -15468,24 +15575,42 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
     <mergeCell ref="M11:M12"/>
     <mergeCell ref="N11:N12"/>
     <mergeCell ref="M8:M9"/>
@@ -15502,42 +15627,24 @@
     <mergeCell ref="H8:H9"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -15803,13 +15910,53 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
@@ -15826,53 +15973,13 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -15893,7 +16000,9 @@
       <c r="B1" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="7"/>
+      <c r="C1" s="7" t="s">
+        <v>122</v>
+      </c>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
@@ -15906,7 +16015,7 @@
       <c r="M1" s="7"/>
       <c r="N1" s="7"/>
     </row>
-    <row r="2" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="23"/>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -15922,7 +16031,7 @@
       <c r="M2" s="15"/>
       <c r="N2" s="15"/>
     </row>
-    <row r="3" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A3" s="24"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -16006,7 +16115,9 @@
       <c r="E7" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F7" s="9"/>
+      <c r="F7" s="7" t="s">
+        <v>121</v>
+      </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
@@ -16022,7 +16133,7 @@
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
-      <c r="F8" s="20"/>
+      <c r="F8" s="15"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
@@ -16038,7 +16149,7 @@
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="21"/>
+      <c r="F9" s="16"/>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
@@ -16155,13 +16266,53 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
@@ -16178,53 +16329,13 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -16483,24 +16594,42 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
     <mergeCell ref="M11:M12"/>
     <mergeCell ref="N11:N12"/>
     <mergeCell ref="M8:M9"/>
@@ -16517,42 +16646,24 @@
     <mergeCell ref="H8:H9"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -17972,30 +18083,52 @@
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="Q11:Q12"/>
-    <mergeCell ref="Q14:Q15"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="P14:P15"/>
-    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="C14:C15"/>
@@ -18012,52 +18145,30 @@
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="E11:E12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="P14:P15"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="P8:P9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -18416,64 +18527,6 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -18486,6 +18539,64 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Excels compiladores de habilidades/Habilidades de criaturas no humanoides.xlsx
+++ b/Excels compiladores de habilidades/Habilidades de criaturas no humanoides.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\arkanor-assets\Excels compiladores de habilidades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E19B80-8EF5-4008-874F-A7259BC75378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203E564D-1191-400D-A04A-3554C52244FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4E5D0542-3908-4101-9CFE-772E035496F2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{4E5D0542-3908-4101-9CFE-772E035496F2}"/>
   </bookViews>
   <sheets>
     <sheet name="No-Muerto" sheetId="8" r:id="rId1"/>
@@ -9494,15 +9494,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9516,6 +9507,15 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12439,15 +12439,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>47224</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>346900</xdr:rowOff>
+      <xdr:colOff>36019</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>10723</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>735267</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>340178</xdr:rowOff>
+      <xdr:colOff>724062</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>4001</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -12476,8 +12476,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6905224" y="346900"/>
-          <a:ext cx="688043" cy="700849"/>
+          <a:off x="6894019" y="358105"/>
+          <a:ext cx="688043" cy="688043"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -12639,13 +12639,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>27214</xdr:colOff>
+      <xdr:colOff>49626</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>13607</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>711214</xdr:colOff>
+      <xdr:colOff>733626</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>343821</xdr:rowOff>
     </xdr:to>
@@ -12676,8 +12676,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5361214" y="3551464"/>
-          <a:ext cx="684000" cy="684000"/>
+          <a:off x="5383626" y="3487431"/>
+          <a:ext cx="684000" cy="677596"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -15333,7 +15333,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17"/>
+      <c r="A1" s="22"/>
       <c r="B1" s="14"/>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -15349,7 +15349,7 @@
       <c r="N1" s="7"/>
     </row>
     <row r="2" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
+      <c r="A2" s="23"/>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
@@ -15365,7 +15365,7 @@
       <c r="N2" s="15"/>
     </row>
     <row r="3" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
+      <c r="A3" s="24"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -15381,7 +15381,7 @@
       <c r="N3" s="16"/>
     </row>
     <row r="4" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20"/>
+      <c r="A4" s="17"/>
       <c r="B4" s="14"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -15397,7 +15397,7 @@
       <c r="N4" s="7"/>
     </row>
     <row r="5" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
+      <c r="A5" s="18"/>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
@@ -15413,7 +15413,7 @@
       <c r="N5" s="15"/>
     </row>
     <row r="6" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
+      <c r="A6" s="19"/>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -15429,7 +15429,7 @@
       <c r="N6" s="16"/>
     </row>
     <row r="7" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -15445,12 +15445,12 @@
       <c r="N7" s="7"/>
     </row>
     <row r="8" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
-      <c r="F8" s="23"/>
+      <c r="F8" s="20"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
@@ -15461,12 +15461,12 @@
       <c r="N8" s="15"/>
     </row>
     <row r="9" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="24"/>
+      <c r="F9" s="21"/>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
@@ -15478,7 +15478,7 @@
       <c r="R9" s="10"/>
     </row>
     <row r="10" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="20"/>
+      <c r="A10" s="17"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -15494,7 +15494,7 @@
       <c r="N10" s="7"/>
     </row>
     <row r="11" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
+      <c r="A11" s="18"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
@@ -15510,7 +15510,7 @@
       <c r="N11" s="15"/>
     </row>
     <row r="12" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
+      <c r="A12" s="19"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
@@ -15526,7 +15526,7 @@
       <c r="N12" s="16"/>
     </row>
     <row r="13" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="9"/>
@@ -15542,7 +15542,7 @@
       <c r="N13" s="7"/>
     </row>
     <row r="14" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
+      <c r="A14" s="18"/>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -15558,7 +15558,342 @@
       <c r="N14" s="15"/>
     </row>
     <row r="15" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="70">
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D5F5BAF-BE93-4F06-A7C2-0B0CBE1C14C1}">
+  <dimension ref="A1:R15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="11.42578125" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+    </row>
+    <row r="2" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="23"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+    </row>
+    <row r="3" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="24"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+    </row>
+    <row r="4" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+    </row>
+    <row r="5" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+    </row>
+    <row r="6" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="19"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+    </row>
+    <row r="7" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="17"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+    </row>
+    <row r="8" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+    </row>
+    <row r="9" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="19"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="R9" s="10"/>
+    </row>
+    <row r="10" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="17"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+    </row>
+    <row r="11" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+    </row>
+    <row r="12" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="19"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+    </row>
+    <row r="13" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="17"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+    </row>
+    <row r="14" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+    </row>
+    <row r="15" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="19"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
@@ -15647,12 +15982,13 @@
     <mergeCell ref="F2:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D5F5BAF-BE93-4F06-A7C2-0B0CBE1C14C1}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9F6337B-89AA-4305-B4A8-6D5D44FBF989}">
   <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -15660,18 +15996,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>116</v>
-      </c>
+      <c r="A1" s="22"/>
       <c r="B1" s="14" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>117</v>
-      </c>
+      <c r="D1" s="7"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
@@ -15684,7 +16016,7 @@
       <c r="N1" s="7"/>
     </row>
     <row r="2" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
+      <c r="A2" s="23"/>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
@@ -15700,7 +16032,7 @@
       <c r="N2" s="15"/>
     </row>
     <row r="3" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
+      <c r="A3" s="24"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -15716,9 +16048,13 @@
       <c r="N3" s="16"/>
     </row>
     <row r="4" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="7"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>109</v>
+      </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
@@ -15732,7 +16068,7 @@
       <c r="N4" s="7"/>
     </row>
     <row r="5" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
+      <c r="A5" s="18"/>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
@@ -15748,7 +16084,7 @@
       <c r="N5" s="15"/>
     </row>
     <row r="6" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
+      <c r="A6" s="19"/>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -15764,7 +16100,355 @@
       <c r="N6" s="16"/>
     </row>
     <row r="7" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20"/>
+      <c r="A7" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+    </row>
+    <row r="8" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+    </row>
+    <row r="9" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="19"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="R9" s="10"/>
+    </row>
+    <row r="10" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="17"/>
+      <c r="B10" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+    </row>
+    <row r="11" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+    </row>
+    <row r="12" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="19"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+    </row>
+    <row r="13" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="17"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+    </row>
+    <row r="14" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+    </row>
+    <row r="15" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="19"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="70">
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{258ECD2D-C047-4967-AAA4-94D91ED5B3F1}">
+  <dimension ref="A1:R15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="11.42578125" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+    </row>
+    <row r="2" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="23"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+    </row>
+    <row r="3" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="24"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+    </row>
+    <row r="4" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+    </row>
+    <row r="5" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+    </row>
+    <row r="6" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="19"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+    </row>
+    <row r="7" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="17"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -15780,12 +16464,12 @@
       <c r="N7" s="7"/>
     </row>
     <row r="8" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
-      <c r="F8" s="23"/>
+      <c r="F8" s="20"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
@@ -15796,12 +16480,12 @@
       <c r="N8" s="15"/>
     </row>
     <row r="9" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="24"/>
+      <c r="F9" s="21"/>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
@@ -15813,7 +16497,7 @@
       <c r="R9" s="10"/>
     </row>
     <row r="10" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="20"/>
+      <c r="A10" s="17"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -15829,7 +16513,7 @@
       <c r="N10" s="7"/>
     </row>
     <row r="11" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
+      <c r="A11" s="18"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
@@ -15845,7 +16529,7 @@
       <c r="N11" s="15"/>
     </row>
     <row r="12" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
+      <c r="A12" s="19"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
@@ -15861,7 +16545,7 @@
       <c r="N12" s="16"/>
     </row>
     <row r="13" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="9"/>
@@ -15877,7 +16561,7 @@
       <c r="N13" s="7"/>
     </row>
     <row r="14" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
+      <c r="A14" s="18"/>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -15893,7 +16577,7 @@
       <c r="N14" s="15"/>
     </row>
     <row r="15" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
+      <c r="A15" s="19"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
@@ -15982,690 +16666,6 @@
     <mergeCell ref="L14:L15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9F6337B-89AA-4305-B4A8-6D5D44FBF989}">
-  <dimension ref="A1:R15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="16384" width="11.42578125" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17"/>
-      <c r="B1" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-    </row>
-    <row r="2" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-    </row>
-    <row r="3" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
-    </row>
-    <row r="4" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20"/>
-      <c r="B4" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-    </row>
-    <row r="5" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-    </row>
-    <row r="6" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-    </row>
-    <row r="7" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-    </row>
-    <row r="8" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-    </row>
-    <row r="9" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="R9" s="10"/>
-    </row>
-    <row r="10" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="20"/>
-      <c r="B10" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-    </row>
-    <row r="11" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-    </row>
-    <row r="12" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-    </row>
-    <row r="13" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-    </row>
-    <row r="14" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-    </row>
-    <row r="15" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-    </row>
-  </sheetData>
-  <mergeCells count="70">
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{258ECD2D-C047-4967-AAA4-94D91ED5B3F1}">
-  <dimension ref="A1:R15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="16384" width="11.42578125" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17"/>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-    </row>
-    <row r="2" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-    </row>
-    <row r="3" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
-    </row>
-    <row r="4" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-    </row>
-    <row r="5" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-    </row>
-    <row r="6" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-    </row>
-    <row r="7" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-    </row>
-    <row r="8" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-    </row>
-    <row r="9" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="R9" s="10"/>
-    </row>
-    <row r="10" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="20"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-    </row>
-    <row r="11" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-    </row>
-    <row r="12" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-    </row>
-    <row r="13" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-    </row>
-    <row r="14" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-    </row>
-    <row r="15" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-    </row>
-  </sheetData>
-  <mergeCells count="70">
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -16679,7 +16679,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
@@ -16718,7 +16718,7 @@
       <c r="Q1" s="7"/>
     </row>
     <row r="2" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="18"/>
+      <c r="A2" s="23"/>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
@@ -16737,7 +16737,7 @@
       <c r="Q2" s="15"/>
     </row>
     <row r="3" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="19"/>
+      <c r="A3" s="24"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -16756,7 +16756,7 @@
       <c r="Q3" s="16"/>
     </row>
     <row r="4" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
@@ -16803,7 +16803,7 @@
       <c r="Q4" s="7"/>
     </row>
     <row r="5" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="21"/>
+      <c r="A5" s="18"/>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
@@ -16822,7 +16822,7 @@
       <c r="Q5" s="15"/>
     </row>
     <row r="6" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="22"/>
+      <c r="A6" s="19"/>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -16841,7 +16841,7 @@
       <c r="Q6" s="16"/>
     </row>
     <row r="7" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="17" t="s">
         <v>1</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -16897,12 +16897,12 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="21"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
-      <c r="F8" s="23"/>
+      <c r="F8" s="20"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
@@ -16917,12 +16917,12 @@
       <c r="R8" s="15"/>
     </row>
     <row r="9" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="22"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="24"/>
+      <c r="F9" s="21"/>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
@@ -16937,7 +16937,7 @@
       <c r="R9" s="16"/>
     </row>
     <row r="10" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="17" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="7" t="s">
@@ -16972,7 +16972,7 @@
       <c r="Q10" s="7"/>
     </row>
     <row r="11" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="21"/>
+      <c r="A11" s="18"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
@@ -16991,7 +16991,7 @@
       <c r="Q11" s="15"/>
     </row>
     <row r="12" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="22"/>
+      <c r="A12" s="19"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
@@ -17010,7 +17010,7 @@
       <c r="Q12" s="16"/>
     </row>
     <row r="13" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="17" t="s">
         <v>59</v>
       </c>
       <c r="B13" s="13" t="s">
@@ -17041,7 +17041,7 @@
       <c r="Q13" s="7"/>
     </row>
     <row r="14" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="21"/>
+      <c r="A14" s="18"/>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -17060,7 +17060,7 @@
       <c r="Q14" s="15"/>
     </row>
     <row r="15" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="22"/>
+      <c r="A15" s="19"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
@@ -18083,30 +18083,52 @@
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="Q11:Q12"/>
-    <mergeCell ref="Q14:Q15"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="P14:P15"/>
-    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="C14:C15"/>
@@ -18123,52 +18145,30 @@
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="E11:E12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="P14:P15"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="P8:P9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -18185,7 +18185,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="22" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="7" t="s">
@@ -18225,7 +18225,7 @@
       <c r="N1" s="7"/>
     </row>
     <row r="2" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
+      <c r="A2" s="23"/>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
@@ -18241,7 +18241,7 @@
       <c r="N2" s="15"/>
     </row>
     <row r="3" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
+      <c r="A3" s="24"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -18257,7 +18257,7 @@
       <c r="N3" s="16"/>
     </row>
     <row r="4" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="17" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="7" t="s">
@@ -18299,7 +18299,7 @@
       <c r="N4" s="7"/>
     </row>
     <row r="5" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
+      <c r="A5" s="18"/>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
@@ -18315,7 +18315,7 @@
       <c r="N5" s="15"/>
     </row>
     <row r="6" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
+      <c r="A6" s="19"/>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -18331,7 +18331,7 @@
       <c r="N6" s="16"/>
     </row>
     <row r="7" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -18359,12 +18359,12 @@
       <c r="N7" s="7"/>
     </row>
     <row r="8" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
-      <c r="F8" s="23"/>
+      <c r="F8" s="20"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
@@ -18375,12 +18375,12 @@
       <c r="N8" s="15"/>
     </row>
     <row r="9" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="24"/>
+      <c r="F9" s="21"/>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
@@ -18392,7 +18392,7 @@
       <c r="R9" s="10"/>
     </row>
     <row r="10" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B10" s="7" t="s">
@@ -18418,7 +18418,7 @@
       <c r="N10" s="7"/>
     </row>
     <row r="11" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
+      <c r="A11" s="18"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
@@ -18434,7 +18434,7 @@
       <c r="N11" s="15"/>
     </row>
     <row r="12" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
+      <c r="A12" s="19"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
@@ -18450,7 +18450,7 @@
       <c r="N12" s="16"/>
     </row>
     <row r="13" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="17" t="s">
         <v>7</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -18494,7 +18494,7 @@
       </c>
     </row>
     <row r="14" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
+      <c r="A14" s="18"/>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -18510,7 +18510,7 @@
       <c r="N14" s="15"/>
     </row>
     <row r="15" spans="1:18" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
+      <c r="A15" s="19"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
@@ -18527,64 +18527,6 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -18597,6 +18539,64 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
